--- a/docs/02) 요구사항정의서.xlsx
+++ b/docs/02) 요구사항정의서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b3e44888da37815c/나연/___사이드프로젝트/웨딩플래너/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\___side_project\wedding-planner\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_0AABBAB32867FC6496C48C78EA44A195A64D857E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A16C12D6-63CF-44C2-B043-0C2D30B63150}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FB4272-ED5D-49AE-A33F-1F60FF0430A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="637">
   <si>
     <t>작성일</t>
   </si>
@@ -2102,25 +2102,10 @@
     <t>개인정보 수정</t>
   </si>
   <si>
-    <t>RM-D01-002</t>
-  </si>
-  <si>
-    <t>RM-D01-003</t>
-  </si>
-  <si>
-    <t>RM-D03-001</t>
-  </si>
-  <si>
     <t>RM-D03-002</t>
   </si>
   <si>
     <t>RM-D03-003</t>
-  </si>
-  <si>
-    <t>RM-D03-004</t>
-  </si>
-  <si>
-    <t>RM-D03-005</t>
   </si>
   <si>
     <t>RM-D04-001</t>
@@ -2178,27 +2163,6 @@
   </si>
   <si>
     <t>로그아웃에 성공하면 로그인 정보가 세션에서 삭제되고 메인 페이지(로그인 창)로 이동한다.</t>
-  </si>
-  <si>
-    <t>RM-D04-002</t>
-  </si>
-  <si>
-    <t>RM-D04-003</t>
-  </si>
-  <si>
-    <t>RM-D06-001</t>
-  </si>
-  <si>
-    <t>RM-D06-003</t>
-  </si>
-  <si>
-    <t>RM-D06-004</t>
-  </si>
-  <si>
-    <t>RM-D06-005</t>
-  </si>
-  <si>
-    <t>RM-D06-006</t>
   </si>
   <si>
     <t>기능</t>
@@ -2322,11 +2286,6 @@
   </si>
   <si>
     <t>카카오톡 계정 인증 버튼을 통해 발급받은 oAuth Access 토큰과 Refresh 토큰은 데이터베이스의 oAuth 테이블에 별도로 저장되어 관리되며 해당 테이블에는 ID가 FK로 참조된다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용자가 로그인 라면 제일 먼저 일정 화면이 조회된다.
-일정 상단에는 결혼식 당일 D-day가 조회되며 아래에는 달력이 조회된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2371,8 +2330,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>일정을 등록하면 짝꿍(신랑 혹은 신부) 모두 해당 일정을 조회할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캘린더 인터페이스는 드래그 앤 드롭 기능을 지원하여 사용자가 이벤트를 새로운 시간대로 이동시켜 일정을 변경할 수 있다. 삭제는 지정된 삭제 영역으로 드래그하거나 삭제 옵션을 사용하여 수행할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RM-C01-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RM-B02-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RM-B02-002</t>
+  </si>
+  <si>
+    <t>RM-B02-003</t>
+  </si>
+  <si>
+    <t>RM-C02-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RM-D01-001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToDo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자(신랑, 신부)가 로그인 하면 가장 먼저 일정 화면이 조회된다.
+일정 상단에는 결혼식 당일 D-day가 조회되며 아래에는 달력이 조회된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">신랑, 신부는 일정 추가 버튼을 클릭하면 새로운 일정을 만들 수 있으며, 
+      <t xml:space="preserve">사용자는 일정 추가 버튼을 클릭하면 새로운 일정을 만들 수 있으며, 
 입력해야 할 세부 사항은 다음과 같다: </t>
     </r>
     <r>
@@ -2422,33 +2420,36 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일정을 등록하면 짝꿍(신랑 혹은 신부) 모두 해당 일정을 조회할 수 있다.</t>
+    <t>ToDoList 관리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>캘린더 인터페이스는 드래그 앤 드롭 기능을 지원하여 사용자가 이벤트를 새로운 시간대로 이동시켜 일정을 변경할 수 있다. 삭제는 지정된 삭제 영역으로 드래그하거나 삭제 옵션을 사용하여 수행할 수 있다.</t>
+    <t>ToDoList 조회</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RM-C01-001</t>
+    <t>RM-D02-001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RM-B02-001</t>
+    <t>내용과 중요도를 설정하여 추가 및 수정할 수 있다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RM-B02-002</t>
-  </si>
-  <si>
-    <t>RM-B02-003</t>
-  </si>
-  <si>
-    <t>RM-C02-001</t>
+    <t>리스트 완료처리를 하면 체크박스 체크, 취소선이 생기며 가장 아래로 내려간다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RM-D01-001</t>
+    <t>완료처리된 리스트를 다시 클릭하면 완료처리가 취소된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자는 완료처리가 되지 않은 순서로 To do list를 조회할 수 있다.
+To do list는 짝꿍이 작성한 리스트까지 포함되어 표시되며, 중요도 순서로 조회된다. 완료처리가 된 리스트는 가장 하단에 표시된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미 작성된 리스트를 수정할 때는 수정 버튼을 누르면 수정창이 열린다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2974,7 +2975,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3032,12 +3033,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79989013336588644"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3822,7 +3817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4087,334 +4082,316 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="9" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="3" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="9" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="3" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="19" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5830,11 +5807,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21">
-      <c r="A1" s="132"/>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
+      <c r="A1" s="128"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
@@ -5855,10 +5832,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="12"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -5867,10 +5844,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="12"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
@@ -5879,10 +5856,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="12"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
@@ -5891,10 +5868,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="12"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
+      <c r="B6" s="129"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -5903,10 +5880,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="12"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -5915,10 +5892,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="12"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
+      <c r="B8" s="129"/>
+      <c r="C8" s="129"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -5927,10 +5904,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="12"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
+      <c r="B9" s="129"/>
+      <c r="C9" s="129"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -5939,10 +5916,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="12"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -5999,10 +5976,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="12"/>
-      <c r="B15" s="130"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
@@ -6011,10 +5988,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="12"/>
-      <c r="B16" s="130"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
@@ -6023,10 +6000,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="12"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -6035,10 +6012,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="12"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
+      <c r="B18" s="129"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
@@ -6047,10 +6024,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="12"/>
-      <c r="B19" s="130"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
+      <c r="B19" s="129"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -6059,10 +6036,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="12"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
+      <c r="B20" s="129"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
@@ -6071,10 +6048,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="12"/>
-      <c r="B21" s="130"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="131"/>
+      <c r="B21" s="129"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -6143,29 +6120,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="B18:C18"/>
@@ -6174,6 +6128,29 @@
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6191,26 +6168,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.25" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="139"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="142" t="s">
+      <c r="B2" s="139"/>
+      <c r="C2" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="144"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="142"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -6235,14 +6212,14 @@
         <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="C4" s="133" t="s">
+        <v>589</v>
+      </c>
+      <c r="C4" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="134"/>
+      <c r="D4" s="132"/>
       <c r="E4" s="5" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="F4" s="5"/>
     </row>
@@ -6251,8 +6228,8 @@
         <v>15</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="134"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
@@ -6261,8 +6238,8 @@
         <v>481</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="134"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="132"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
@@ -6271,8 +6248,8 @@
         <v>498</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
+      <c r="C7" s="133"/>
+      <c r="D7" s="134"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
@@ -6470,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="2" width="15.69921875" style="1" customWidth="1"/>
@@ -6484,33 +6461,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
       <c r="I1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="120"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="125"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="127"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="108"/>
     </row>
     <row r="3" spans="1:9" ht="39.9" customHeight="1">
       <c r="A3" s="36" t="s">
@@ -6523,139 +6500,139 @@
         <v>3</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="85" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="G3" s="85" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="109" t="s">
         <v>560</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="128" t="s">
+      <c r="C4" s="112" t="s">
         <v>556</v>
       </c>
-      <c r="D4" s="89" t="s">
-        <v>606</v>
+      <c r="D4" s="88" t="s">
+        <v>594</v>
       </c>
       <c r="E4" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F4" s="89" t="s">
         <v>576</v>
-      </c>
-      <c r="F4" s="91" t="s">
-        <v>581</v>
       </c>
       <c r="G4" s="75"/>
       <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:9" ht="38.4">
-      <c r="A5" s="108"/>
+      <c r="A5" s="110"/>
       <c r="B5" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="129"/>
-      <c r="D5" s="89" t="s">
-        <v>602</v>
+      <c r="C5" s="113"/>
+      <c r="D5" s="88" t="s">
+        <v>590</v>
       </c>
       <c r="E5" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F5" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F5" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G5" s="91" t="s">
-        <v>581</v>
+      <c r="G5" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H5" s="84"/>
     </row>
     <row r="6" spans="1:9" ht="38.4">
-      <c r="A6" s="108"/>
+      <c r="A6" s="110"/>
       <c r="B6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="129"/>
-      <c r="D6" s="89" t="s">
-        <v>604</v>
+      <c r="C6" s="113"/>
+      <c r="D6" s="88" t="s">
+        <v>592</v>
       </c>
       <c r="E6" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F6" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F6" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G6" s="91" t="s">
-        <v>581</v>
+      <c r="G6" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H6" s="86"/>
     </row>
     <row r="7" spans="1:9" ht="57.6">
-      <c r="A7" s="108"/>
+      <c r="A7" s="110"/>
       <c r="B7" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="129"/>
-      <c r="D7" s="89" t="s">
-        <v>625</v>
+      <c r="C7" s="113"/>
+      <c r="D7" s="88" t="s">
+        <v>613</v>
       </c>
       <c r="E7" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F7" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F7" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G7" s="91" t="s">
-        <v>581</v>
+      <c r="G7" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H7" s="86"/>
     </row>
     <row r="8" spans="1:9" ht="20.399999999999999">
-      <c r="A8" s="108"/>
+      <c r="A8" s="110"/>
       <c r="B8" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="129"/>
-      <c r="D8" s="89" t="s">
-        <v>605</v>
+      <c r="C8" s="113"/>
+      <c r="D8" s="88" t="s">
+        <v>593</v>
       </c>
       <c r="E8" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F8" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F8" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G8" s="91" t="s">
-        <v>581</v>
+      <c r="G8" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H8" s="84"/>
     </row>
     <row r="9" spans="1:9" ht="20.399999999999999">
-      <c r="A9" s="108"/>
+      <c r="A9" s="110"/>
       <c r="B9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="114" t="s">
         <v>557</v>
       </c>
-      <c r="D9" s="89" t="s">
-        <v>607</v>
+      <c r="D9" s="88" t="s">
+        <v>595</v>
       </c>
       <c r="E9" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F9" s="89" t="s">
         <v>576</v>
-      </c>
-      <c r="F9" s="91" t="s">
-        <v>581</v>
       </c>
       <c r="G9" s="87" t="s">
         <v>322</v>
@@ -6663,275 +6640,275 @@
       <c r="H9" s="84"/>
     </row>
     <row r="10" spans="1:9" ht="57.6">
-      <c r="A10" s="108"/>
+      <c r="A10" s="110"/>
       <c r="B10" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="89" t="s">
-        <v>608</v>
+      <c r="C10" s="115"/>
+      <c r="D10" s="88" t="s">
+        <v>596</v>
       </c>
       <c r="E10" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F10" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F10" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G10" s="91" t="s">
-        <v>581</v>
+      <c r="G10" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H10" s="84"/>
     </row>
     <row r="11" spans="1:9" ht="76.8">
-      <c r="A11" s="108"/>
+      <c r="A11" s="110"/>
       <c r="B11" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="89" t="s">
-        <v>609</v>
+      <c r="C11" s="115"/>
+      <c r="D11" s="88" t="s">
+        <v>597</v>
       </c>
       <c r="E11" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F11" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F11" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G11" s="91" t="s">
-        <v>581</v>
+      <c r="G11" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H11" s="84"/>
     </row>
     <row r="12" spans="1:9" ht="76.8">
-      <c r="A12" s="108"/>
+      <c r="A12" s="110"/>
       <c r="B12" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="97"/>
-      <c r="D12" s="89" t="s">
-        <v>610</v>
+      <c r="C12" s="115"/>
+      <c r="D12" s="88" t="s">
+        <v>598</v>
       </c>
       <c r="E12" s="83" t="s">
+        <v>571</v>
+      </c>
+      <c r="F12" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F12" s="91" t="s">
-        <v>581</v>
-      </c>
-      <c r="G12" s="91" t="s">
-        <v>581</v>
+      <c r="G12" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="H12" s="84"/>
     </row>
     <row r="13" spans="1:9" ht="38.4">
-      <c r="A13" s="108"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="97"/>
-      <c r="D13" s="89" t="s">
-        <v>611</v>
+      <c r="C13" s="115"/>
+      <c r="D13" s="88" t="s">
+        <v>599</v>
       </c>
       <c r="E13" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="F13" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F13" s="91" t="s">
-        <v>581</v>
-      </c>
       <c r="G13" s="73" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H13" s="38"/>
     </row>
     <row r="14" spans="1:9" ht="38.4">
-      <c r="A14" s="108"/>
+      <c r="A14" s="110"/>
       <c r="B14" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="97"/>
-      <c r="D14" s="89" t="s">
-        <v>585</v>
+      <c r="C14" s="115"/>
+      <c r="D14" s="88" t="s">
+        <v>580</v>
       </c>
       <c r="E14" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="F14" s="89" t="s">
         <v>576</v>
       </c>
-      <c r="F14" s="91" t="s">
-        <v>581</v>
-      </c>
       <c r="G14" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H14" s="38"/>
     </row>
     <row r="15" spans="1:9" ht="20.399999999999999">
-      <c r="A15" s="108"/>
+      <c r="A15" s="110"/>
       <c r="B15" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="97"/>
-      <c r="D15" s="89" t="s">
-        <v>612</v>
+      <c r="C15" s="115"/>
+      <c r="D15" s="88" t="s">
+        <v>600</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="F15" s="91" t="s">
-        <v>581</v>
+        <v>572</v>
+      </c>
+      <c r="F15" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:9" ht="57.6">
-      <c r="A16" s="108"/>
+      <c r="A16" s="110"/>
       <c r="B16" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="89" t="s">
-        <v>613</v>
+      <c r="C16" s="116"/>
+      <c r="D16" s="88" t="s">
+        <v>601</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>577</v>
-      </c>
-      <c r="F16" s="91" t="s">
-        <v>581</v>
+        <v>572</v>
+      </c>
+      <c r="F16" s="89" t="s">
+        <v>576</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H16" s="38"/>
     </row>
     <row r="17" spans="1:8" ht="20.399999999999999">
-      <c r="A17" s="108"/>
+      <c r="A17" s="110"/>
       <c r="B17" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="114" t="s">
         <v>558</v>
       </c>
-      <c r="D17" s="89" t="s">
-        <v>614</v>
+      <c r="D17" s="88" t="s">
+        <v>602</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H17" s="38"/>
     </row>
     <row r="18" spans="1:8" ht="38.4">
-      <c r="A18" s="108"/>
+      <c r="A18" s="110"/>
       <c r="B18" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="97"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="77" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F18" s="25"/>
       <c r="G18" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" ht="20.399999999999999">
-      <c r="A19" s="108"/>
+      <c r="A19" s="110"/>
       <c r="B19" s="30" t="s">
-        <v>597</v>
-      </c>
-      <c r="C19" s="95" t="s">
-        <v>595</v>
+        <v>585</v>
+      </c>
+      <c r="C19" s="114" t="s">
+        <v>583</v>
       </c>
       <c r="D19" s="77" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>322</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="H19" s="38"/>
     </row>
     <row r="20" spans="1:8" ht="20.399999999999999">
-      <c r="A20" s="108"/>
+      <c r="A20" s="110"/>
       <c r="B20" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="97"/>
+      <c r="C20" s="115"/>
       <c r="D20" s="77" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>322</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="H20" s="38"/>
     </row>
     <row r="21" spans="1:8" ht="20.399999999999999">
-      <c r="A21" s="109"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="C21" s="96"/>
+        <v>587</v>
+      </c>
+      <c r="C21" s="116"/>
       <c r="D21" s="77" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>322</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H21" s="38"/>
     </row>
     <row r="22" spans="1:8" ht="57.6">
-      <c r="A22" s="116" t="s">
-        <v>617</v>
+      <c r="A22" s="97" t="s">
+        <v>605</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>559</v>
       </c>
-      <c r="C22" s="95" t="s">
+      <c r="C22" s="114" t="s">
         <v>561</v>
       </c>
       <c r="D22" s="78" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F22" s="25"/>
       <c r="G22" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H22" s="38"/>
     </row>
     <row r="23" spans="1:8" ht="76.8">
-      <c r="A23" s="117"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="116"/>
       <c r="D23" s="78" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>24</v>
@@ -6941,15 +6918,15 @@
       <c r="H23" s="38"/>
     </row>
     <row r="24" spans="1:8" ht="57.6">
-      <c r="A24" s="117"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="30" t="s">
-        <v>635</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>620</v>
+        <v>621</v>
+      </c>
+      <c r="C24" s="114" t="s">
+        <v>608</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>24</v>
@@ -6959,13 +6936,13 @@
       <c r="H24" s="38"/>
     </row>
     <row r="25" spans="1:8" ht="38.4">
-      <c r="A25" s="117"/>
+      <c r="A25" s="98"/>
       <c r="B25" s="30" t="s">
-        <v>636</v>
-      </c>
-      <c r="C25" s="97"/>
+        <v>622</v>
+      </c>
+      <c r="C25" s="115"/>
       <c r="D25" s="78" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>24</v>
@@ -6975,145 +6952,145 @@
       <c r="H25" s="38"/>
     </row>
     <row r="26" spans="1:8" ht="57.6">
-      <c r="A26" s="117"/>
+      <c r="A26" s="98"/>
       <c r="B26" s="30" t="s">
-        <v>637</v>
-      </c>
-      <c r="C26" s="96"/>
+        <v>623</v>
+      </c>
+      <c r="C26" s="116"/>
       <c r="D26" s="78" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F26" s="25"/>
       <c r="G26" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8" ht="38.4">
-      <c r="A27" s="107" t="s">
-        <v>624</v>
+      <c r="A27" s="109" t="s">
+        <v>612</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>634</v>
-      </c>
-      <c r="C27" s="115" t="s">
-        <v>583</v>
+        <v>620</v>
+      </c>
+      <c r="C27" s="117" t="s">
+        <v>578</v>
       </c>
       <c r="D27" s="81" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F27" s="25"/>
       <c r="G27" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H27" s="38"/>
     </row>
     <row r="28" spans="1:8" ht="38.4">
-      <c r="A28" s="108"/>
+      <c r="A28" s="110"/>
       <c r="B28" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C28" s="105"/>
-      <c r="D28" s="189" t="s">
-        <v>627</v>
+      <c r="C28" s="118"/>
+      <c r="D28" s="91" t="s">
+        <v>614</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>520</v>
       </c>
       <c r="F28" s="25"/>
       <c r="G28" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H28" s="38"/>
     </row>
     <row r="29" spans="1:8" ht="38.4">
-      <c r="A29" s="108"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="C29" s="105"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="81" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H29" s="38"/>
     </row>
     <row r="30" spans="1:8" ht="38.4">
-      <c r="A30" s="108"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C30" s="105"/>
-      <c r="D30" s="190" t="s">
-        <v>628</v>
+      <c r="C30" s="118"/>
+      <c r="D30" s="92" t="s">
+        <v>615</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F30" s="25"/>
       <c r="G30" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8" ht="57.6">
-      <c r="A31" s="108"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="C31" s="197"/>
-      <c r="D31" s="191" t="s">
-        <v>629</v>
+      <c r="C31" s="119"/>
+      <c r="D31" s="93" t="s">
+        <v>616</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F31" s="25"/>
       <c r="G31" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H31" s="38"/>
     </row>
     <row r="32" spans="1:8" ht="76.8">
-      <c r="A32" s="108"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="30" t="s">
-        <v>638</v>
-      </c>
-      <c r="C32" s="195" t="s">
-        <v>582</v>
-      </c>
-      <c r="D32" s="192" t="s">
-        <v>631</v>
+        <v>624</v>
+      </c>
+      <c r="C32" s="120" t="s">
+        <v>577</v>
+      </c>
+      <c r="D32" s="94" t="s">
+        <v>628</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F32" s="25"/>
       <c r="G32" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H32" s="38"/>
     </row>
     <row r="33" spans="1:9" ht="20.399999999999999">
-      <c r="A33" s="108"/>
+      <c r="A33" s="110"/>
       <c r="B33" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="C33" s="164"/>
-      <c r="D33" s="192" t="s">
-        <v>632</v>
+      <c r="C33" s="121"/>
+      <c r="D33" s="94" t="s">
+        <v>618</v>
       </c>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
@@ -7121,433 +7098,247 @@
       <c r="H33" s="38"/>
     </row>
     <row r="34" spans="1:9" ht="57.6">
-      <c r="A34" s="108"/>
+      <c r="A34" s="110"/>
       <c r="B34" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="C34" s="164"/>
-      <c r="D34" s="193" t="s">
-        <v>633</v>
+      <c r="C34" s="121"/>
+      <c r="D34" s="95" t="s">
+        <v>619</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H34" s="38"/>
       <c r="I34" s="19"/>
     </row>
     <row r="35" spans="1:9" ht="38.4">
-      <c r="A35" s="108"/>
+      <c r="A35" s="110"/>
       <c r="B35" s="30" t="s">
         <v>369</v>
       </c>
-      <c r="C35" s="164"/>
-      <c r="D35" s="192" t="s">
-        <v>630</v>
+      <c r="C35" s="121"/>
+      <c r="D35" s="94" t="s">
+        <v>617</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F35" s="25"/>
       <c r="G35" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H35" s="38"/>
     </row>
     <row r="36" spans="1:9" ht="38.4">
-      <c r="A36" s="108"/>
+      <c r="A36" s="110"/>
       <c r="B36" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C36" s="164"/>
-      <c r="D36" s="194" t="s">
-        <v>584</v>
+      <c r="C36" s="121"/>
+      <c r="D36" s="96" t="s">
+        <v>579</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F36" s="25"/>
       <c r="G36" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H36" s="38"/>
     </row>
     <row r="37" spans="1:9" ht="57.6">
-      <c r="A37" s="109"/>
+      <c r="A37" s="111"/>
       <c r="B37" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="C37" s="196"/>
-      <c r="D37" s="193" t="s">
-        <v>575</v>
+      <c r="C37" s="122"/>
+      <c r="D37" s="95" t="s">
+        <v>570</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F37" s="25"/>
       <c r="G37" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H37" s="38"/>
     </row>
-    <row r="38" spans="1:9" ht="20.399999999999999">
-      <c r="A38" s="188"/>
-      <c r="B38" s="94" t="s">
-        <v>639</v>
-      </c>
-      <c r="C38" s="186"/>
-      <c r="D38" s="79"/>
+    <row r="38" spans="1:9" ht="57.6">
+      <c r="A38" s="109" t="s">
+        <v>626</v>
+      </c>
+      <c r="B38" s="90" t="s">
+        <v>625</v>
+      </c>
+      <c r="C38" s="191" t="s">
+        <v>630</v>
+      </c>
+      <c r="D38" s="79" t="s">
+        <v>635</v>
+      </c>
       <c r="E38" s="25" t="s">
         <v>24</v>
       </c>
       <c r="F38" s="25"/>
       <c r="G38" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H38" s="38"/>
     </row>
     <row r="39" spans="1:9" ht="20.399999999999999">
-      <c r="A39" s="188"/>
-      <c r="B39" s="94" t="s">
-        <v>562</v>
-      </c>
-      <c r="C39" s="186"/>
-      <c r="D39" s="88"/>
+      <c r="A39" s="110"/>
+      <c r="B39" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="C39" s="125" t="s">
+        <v>629</v>
+      </c>
+      <c r="D39" s="190" t="s">
+        <v>632</v>
+      </c>
       <c r="E39" s="25" t="s">
-        <v>24</v>
+        <v>571</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H39" s="38"/>
     </row>
     <row r="40" spans="1:9" ht="20.399999999999999">
-      <c r="A40" s="188"/>
-      <c r="B40" s="94" t="s">
-        <v>563</v>
-      </c>
-      <c r="C40" s="187"/>
-      <c r="D40" s="79"/>
+      <c r="A40" s="110"/>
+      <c r="B40" s="30" t="s">
+        <v>562</v>
+      </c>
+      <c r="C40" s="126"/>
+      <c r="D40" s="79" t="s">
+        <v>636</v>
+      </c>
       <c r="E40" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F40" s="25"/>
       <c r="G40" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H40" s="38"/>
     </row>
-    <row r="41" spans="1:9" ht="20.399999999999999">
-      <c r="A41" s="188"/>
+    <row r="41" spans="1:9" ht="39.450000000000003" customHeight="1">
+      <c r="A41" s="110"/>
       <c r="B41" s="30" t="s">
-        <v>564</v>
-      </c>
-      <c r="C41" s="111"/>
-      <c r="D41" s="79"/>
+        <v>563</v>
+      </c>
+      <c r="C41" s="126"/>
+      <c r="D41" s="79" t="s">
+        <v>633</v>
+      </c>
       <c r="E41" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F41" s="25"/>
       <c r="G41" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H41" s="38"/>
     </row>
     <row r="42" spans="1:9" ht="20.399999999999999">
-      <c r="A42" s="188"/>
+      <c r="A42" s="111"/>
       <c r="B42" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="C42" s="112"/>
-      <c r="D42" s="79"/>
+        <v>564</v>
+      </c>
+      <c r="C42" s="127"/>
+      <c r="D42" s="79" t="s">
+        <v>634</v>
+      </c>
       <c r="E42" s="25" t="s">
-        <v>576</v>
+        <v>520</v>
       </c>
       <c r="F42" s="25"/>
       <c r="G42" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H42" s="38"/>
     </row>
-    <row r="43" spans="1:9" ht="39.450000000000003" customHeight="1">
-      <c r="A43" s="188"/>
+    <row r="43" spans="1:9" ht="20.399999999999999">
+      <c r="A43" s="109"/>
       <c r="B43" s="30" t="s">
-        <v>566</v>
-      </c>
-      <c r="C43" s="112"/>
-      <c r="D43" s="79"/>
+        <v>565</v>
+      </c>
+      <c r="C43" s="123"/>
+      <c r="D43" s="80"/>
       <c r="E43" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F43" s="25"/>
       <c r="G43" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H43" s="38"/>
     </row>
     <row r="44" spans="1:9" ht="20.399999999999999">
-      <c r="A44" s="188"/>
+      <c r="A44" s="110"/>
       <c r="B44" s="30" t="s">
-        <v>567</v>
-      </c>
-      <c r="C44" s="112"/>
-      <c r="D44" s="79"/>
+        <v>566</v>
+      </c>
+      <c r="C44" s="118"/>
+      <c r="D44" s="76"/>
       <c r="E44" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F44" s="25"/>
       <c r="G44" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H44" s="38"/>
-      <c r="I44" s="24"/>
     </row>
     <row r="45" spans="1:9" ht="20.399999999999999">
-      <c r="A45" s="188"/>
+      <c r="A45" s="110"/>
       <c r="B45" s="30" t="s">
-        <v>568</v>
-      </c>
-      <c r="C45" s="113"/>
-      <c r="D45" s="79"/>
+        <v>567</v>
+      </c>
+      <c r="C45" s="118"/>
+      <c r="D45" s="76"/>
       <c r="E45" s="25" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F45" s="25"/>
       <c r="G45" s="25" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H45" s="38"/>
     </row>
     <row r="46" spans="1:9" ht="20.399999999999999">
-      <c r="A46" s="188"/>
+      <c r="A46" s="111"/>
       <c r="B46" s="30" t="s">
-        <v>569</v>
-      </c>
-      <c r="C46" s="112"/>
-      <c r="D46" s="79"/>
+        <v>568</v>
+      </c>
+      <c r="C46" s="124"/>
+      <c r="D46" s="77"/>
       <c r="E46" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25" t="s">
-        <v>581</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="G46" s="25"/>
       <c r="H46" s="38"/>
     </row>
-    <row r="47" spans="1:9" ht="57.75" customHeight="1">
-      <c r="A47" s="188"/>
-      <c r="B47" s="30" t="s">
-        <v>587</v>
-      </c>
-      <c r="C47" s="112"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H47" s="38"/>
-    </row>
-    <row r="48" spans="1:9" ht="38.25" customHeight="1">
-      <c r="A48" s="188"/>
-      <c r="B48" s="30" t="s">
-        <v>588</v>
-      </c>
-      <c r="C48" s="113"/>
-      <c r="D48" s="90"/>
-      <c r="E48" s="93" t="s">
-        <v>520</v>
-      </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H48" s="38"/>
-    </row>
-    <row r="49" spans="1:8" ht="38.25" customHeight="1">
-      <c r="A49" s="188"/>
-      <c r="B49" s="30" t="s">
-        <v>503</v>
-      </c>
-      <c r="C49" s="92"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="25" t="s">
-        <v>520</v>
-      </c>
-      <c r="F49" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="G49" s="25"/>
-      <c r="H49" s="38"/>
-    </row>
-    <row r="50" spans="1:8" ht="20.399999999999999">
-      <c r="A50" s="188"/>
-      <c r="B50" s="30" t="s">
-        <v>589</v>
-      </c>
-      <c r="C50" s="111"/>
-      <c r="D50" s="79"/>
-      <c r="E50" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H50" s="38"/>
-    </row>
-    <row r="51" spans="1:8" ht="20.399999999999999">
-      <c r="A51" s="188"/>
-      <c r="B51" s="30" t="s">
-        <v>509</v>
-      </c>
-      <c r="C51" s="110"/>
-      <c r="D51" s="79"/>
-      <c r="E51" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H51" s="38"/>
-    </row>
-    <row r="52" spans="1:8" ht="20.399999999999999">
-      <c r="A52" s="188"/>
-      <c r="B52" s="30" t="s">
-        <v>590</v>
-      </c>
-      <c r="C52" s="110"/>
-      <c r="D52" s="79"/>
-      <c r="E52" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H52" s="38"/>
-    </row>
-    <row r="53" spans="1:8" ht="20.399999999999999">
-      <c r="A53" s="188"/>
-      <c r="B53" s="30" t="s">
-        <v>591</v>
-      </c>
-      <c r="C53" s="110"/>
-      <c r="D53" s="79"/>
-      <c r="E53" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H53" s="38"/>
-    </row>
-    <row r="54" spans="1:8" ht="20.399999999999999">
-      <c r="A54" s="188"/>
-      <c r="B54" s="30" t="s">
-        <v>592</v>
-      </c>
-      <c r="C54" s="110"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H54" s="38"/>
-    </row>
-    <row r="55" spans="1:8" ht="20.399999999999999">
-      <c r="A55" s="188"/>
-      <c r="B55" s="30" t="s">
-        <v>593</v>
-      </c>
-      <c r="C55" s="110"/>
-      <c r="D55" s="79"/>
-      <c r="E55" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H55" s="38"/>
-    </row>
-    <row r="56" spans="1:8" ht="20.399999999999999">
-      <c r="A56" s="107"/>
-      <c r="B56" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="C56" s="104"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H56" s="38"/>
-    </row>
-    <row r="57" spans="1:8" ht="20.399999999999999">
-      <c r="A57" s="108"/>
-      <c r="B57" s="30" t="s">
-        <v>571</v>
-      </c>
-      <c r="C57" s="105"/>
-      <c r="D57" s="76"/>
-      <c r="E57" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H57" s="38"/>
-    </row>
-    <row r="58" spans="1:8" ht="20.399999999999999">
-      <c r="A58" s="108"/>
-      <c r="B58" s="30" t="s">
-        <v>572</v>
-      </c>
-      <c r="C58" s="105"/>
-      <c r="D58" s="76"/>
-      <c r="E58" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25" t="s">
-        <v>581</v>
-      </c>
-      <c r="H58" s="38"/>
-    </row>
-    <row r="59" spans="1:8" ht="20.399999999999999">
-      <c r="A59" s="109"/>
-      <c r="B59" s="30" t="s">
-        <v>573</v>
-      </c>
-      <c r="C59" s="106"/>
-      <c r="D59" s="77"/>
-      <c r="E59" s="25" t="s">
-        <v>576</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="G59" s="25"/>
-      <c r="H59" s="38"/>
-    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="C32:C37"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="A27:A37"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="C39:C42"/>
     <mergeCell ref="A22:A26"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
@@ -7558,14 +7349,6 @@
     <mergeCell ref="C9:C16"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="C32:C37"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C50:C55"/>
-    <mergeCell ref="A27:A37"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C26"/>
   </mergeCells>
@@ -7590,27 +7373,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="120"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
       <c r="G1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
@@ -7639,13 +7422,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="52.2">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="145" t="s">
         <v>169</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="152" t="s">
+      <c r="C4" s="147" t="s">
         <v>162</v>
       </c>
       <c r="D4" s="41" t="s">
@@ -7659,11 +7442,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="34.799999999999997">
-      <c r="A5" s="151"/>
+      <c r="A5" s="146"/>
       <c r="B5" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="152"/>
+      <c r="C5" s="147"/>
       <c r="D5" s="41" t="s">
         <v>170</v>
       </c>
@@ -7675,39 +7458,39 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="69.599999999999994">
-      <c r="A6" s="151"/>
+      <c r="A6" s="146"/>
       <c r="B6" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="152"/>
+      <c r="C6" s="147"/>
       <c r="D6" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="153" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="153" t="s">
+      <c r="E6" s="148" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="148" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A7" s="151"/>
+      <c r="A7" s="146"/>
       <c r="B7" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="152"/>
+      <c r="C7" s="147"/>
       <c r="D7" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="148"/>
     </row>
     <row r="8" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A8" s="151"/>
+      <c r="A8" s="146"/>
       <c r="B8" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="152"/>
+      <c r="C8" s="147"/>
       <c r="D8" s="42" t="s">
         <v>172</v>
       </c>
@@ -7719,11 +7502,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A9" s="151"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="152"/>
+      <c r="C9" s="147"/>
       <c r="D9" s="43" t="s">
         <v>412</v>
       </c>
@@ -7738,11 +7521,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="34.799999999999997">
-      <c r="A10" s="151"/>
+      <c r="A10" s="146"/>
       <c r="B10" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="152"/>
+      <c r="C10" s="147"/>
       <c r="D10" s="44" t="s">
         <v>413</v>
       </c>
@@ -7755,11 +7538,11 @@
       <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A11" s="151"/>
+      <c r="A11" s="146"/>
       <c r="B11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="152"/>
+      <c r="C11" s="147"/>
       <c r="D11" s="42" t="s">
         <v>174</v>
       </c>
@@ -7771,12 +7554,12 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A12" s="151"/>
+      <c r="A12" s="146"/>
       <c r="B12" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="152"/>
-      <c r="D12" s="154" t="s">
+      <c r="C12" s="147"/>
+      <c r="D12" s="149" t="s">
         <v>176</v>
       </c>
       <c r="E12" s="25" t="s">
@@ -7787,12 +7570,12 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A13" s="151"/>
+      <c r="A13" s="146"/>
       <c r="B13" s="30" t="s">
         <v>529</v>
       </c>
-      <c r="C13" s="152"/>
-      <c r="D13" s="154"/>
+      <c r="C13" s="147"/>
+      <c r="D13" s="149"/>
       <c r="E13" s="25" t="s">
         <v>24</v>
       </c>
@@ -7801,11 +7584,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="104.4">
-      <c r="A14" s="151"/>
+      <c r="A14" s="146"/>
       <c r="B14" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="152"/>
+      <c r="C14" s="147"/>
       <c r="D14" s="41" t="s">
         <v>305</v>
       </c>
@@ -7817,11 +7600,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="90.75" customHeight="1">
-      <c r="A15" s="151"/>
+      <c r="A15" s="146"/>
       <c r="B15" s="30" t="s">
         <v>528</v>
       </c>
-      <c r="C15" s="152"/>
+      <c r="C15" s="147"/>
       <c r="D15" s="41" t="s">
         <v>177</v>
       </c>
@@ -7833,11 +7616,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A16" s="151"/>
+      <c r="A16" s="146"/>
       <c r="B16" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="150" t="s">
         <v>184</v>
       </c>
       <c r="D16" s="42" t="s">
@@ -7851,11 +7634,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A17" s="151"/>
+      <c r="A17" s="146"/>
       <c r="B17" s="30" t="s">
         <v>533</v>
       </c>
-      <c r="C17" s="155"/>
+      <c r="C17" s="150"/>
       <c r="D17" s="41" t="s">
         <v>179</v>
       </c>
@@ -7867,11 +7650,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="60" customHeight="1">
-      <c r="A18" s="151"/>
+      <c r="A18" s="146"/>
       <c r="B18" s="30" t="s">
         <v>531</v>
       </c>
-      <c r="C18" s="155"/>
+      <c r="C18" s="150"/>
       <c r="D18" s="41" t="s">
         <v>185</v>
       </c>
@@ -7883,11 +7666,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A19" s="151"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="30" t="s">
         <v>536</v>
       </c>
-      <c r="C19" s="155"/>
+      <c r="C19" s="150"/>
       <c r="D19" s="41" t="s">
         <v>187</v>
       </c>
@@ -7899,11 +7682,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A20" s="151"/>
+      <c r="A20" s="146"/>
       <c r="B20" s="30" t="s">
         <v>539</v>
       </c>
-      <c r="C20" s="155"/>
+      <c r="C20" s="150"/>
       <c r="D20" s="42" t="s">
         <v>188</v>
       </c>
@@ -7915,11 +7698,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="52.2">
-      <c r="A21" s="151"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="155"/>
+      <c r="C21" s="150"/>
       <c r="D21" s="41" t="s">
         <v>186</v>
       </c>
@@ -7931,11 +7714,11 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="55.2" customHeight="1">
-      <c r="A22" s="151"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="30" t="s">
         <v>534</v>
       </c>
-      <c r="C22" s="155"/>
+      <c r="C22" s="150"/>
       <c r="D22" s="41" t="s">
         <v>189</v>
       </c>
@@ -7947,11 +7730,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="45" customHeight="1">
-      <c r="A23" s="151"/>
+      <c r="A23" s="146"/>
       <c r="B23" s="30" t="s">
         <v>537</v>
       </c>
-      <c r="C23" s="155"/>
+      <c r="C23" s="150"/>
       <c r="D23" s="41" t="s">
         <v>190</v>
       </c>
@@ -7963,11 +7746,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A24" s="151"/>
+      <c r="A24" s="146"/>
       <c r="B24" s="30" t="s">
         <v>540</v>
       </c>
-      <c r="C24" s="155"/>
+      <c r="C24" s="150"/>
       <c r="D24" s="41" t="s">
         <v>191</v>
       </c>
@@ -7979,11 +7762,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="60" customHeight="1">
-      <c r="A25" s="151"/>
+      <c r="A25" s="146"/>
       <c r="B25" s="30" t="s">
         <v>532</v>
       </c>
-      <c r="C25" s="155"/>
+      <c r="C25" s="150"/>
       <c r="D25" s="41" t="s">
         <v>192</v>
       </c>
@@ -7995,11 +7778,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="60" customHeight="1">
-      <c r="A26" s="151"/>
+      <c r="A26" s="146"/>
       <c r="B26" s="30" t="s">
         <v>530</v>
       </c>
-      <c r="C26" s="155"/>
+      <c r="C26" s="150"/>
       <c r="D26" s="41" t="s">
         <v>193</v>
       </c>
@@ -8011,11 +7794,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="45" customHeight="1">
-      <c r="A27" s="151"/>
+      <c r="A27" s="146"/>
       <c r="B27" s="30" t="s">
         <v>535</v>
       </c>
-      <c r="C27" s="155"/>
+      <c r="C27" s="150"/>
       <c r="D27" s="41" t="s">
         <v>194</v>
       </c>
@@ -8027,11 +7810,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="45" customHeight="1">
-      <c r="A28" s="151"/>
+      <c r="A28" s="146"/>
       <c r="B28" s="30" t="s">
         <v>538</v>
       </c>
-      <c r="C28" s="155"/>
+      <c r="C28" s="150"/>
       <c r="D28" s="41" t="s">
         <v>195</v>
       </c>
@@ -8043,11 +7826,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="90" customHeight="1">
-      <c r="A29" s="151"/>
+      <c r="A29" s="146"/>
       <c r="B29" s="30" t="s">
         <v>542</v>
       </c>
-      <c r="C29" s="155" t="s">
+      <c r="C29" s="150" t="s">
         <v>196</v>
       </c>
       <c r="D29" s="41" t="s">
@@ -8064,11 +7847,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A30" s="151"/>
+      <c r="A30" s="146"/>
       <c r="B30" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="155"/>
+      <c r="C30" s="150"/>
       <c r="D30" s="41" t="s">
         <v>199</v>
       </c>
@@ -8080,11 +7863,11 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="42" customHeight="1">
-      <c r="A31" s="151"/>
+      <c r="A31" s="146"/>
       <c r="B31" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="155"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="41" t="s">
         <v>200</v>
       </c>
@@ -8096,11 +7879,11 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A32" s="151"/>
+      <c r="A32" s="146"/>
       <c r="B32" s="30" t="s">
         <v>543</v>
       </c>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="151" t="s">
         <v>49</v>
       </c>
       <c r="D32" s="41" t="s">
@@ -8114,11 +7897,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.2" customHeight="1">
-      <c r="A33" s="151"/>
+      <c r="A33" s="146"/>
       <c r="B33" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="145"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="41" t="s">
         <v>202</v>
       </c>
@@ -8130,11 +7913,11 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="60" customHeight="1">
-      <c r="A34" s="151"/>
+      <c r="A34" s="146"/>
       <c r="B34" s="30" t="s">
         <v>544</v>
       </c>
-      <c r="C34" s="145" t="s">
+      <c r="C34" s="151" t="s">
         <v>52</v>
       </c>
       <c r="D34" s="41" t="s">
@@ -8148,11 +7931,11 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="104.4">
-      <c r="A35" s="151"/>
+      <c r="A35" s="146"/>
       <c r="B35" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="145"/>
+      <c r="C35" s="151"/>
       <c r="D35" s="41" t="s">
         <v>332</v>
       </c>
@@ -8164,11 +7947,11 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="87">
-      <c r="A36" s="151"/>
+      <c r="A36" s="146"/>
       <c r="B36" s="30" t="s">
         <v>547</v>
       </c>
-      <c r="C36" s="145"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="41" t="s">
         <v>331</v>
       </c>
@@ -8180,11 +7963,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="30" t="s">
         <v>545</v>
       </c>
-      <c r="C37" s="145"/>
+      <c r="C37" s="151"/>
       <c r="D37" s="42" t="s">
         <v>204</v>
       </c>
@@ -8194,11 +7977,11 @@
       <c r="F37" s="25"/>
     </row>
     <row r="38" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A38" s="151"/>
+      <c r="A38" s="146"/>
       <c r="B38" s="30" t="s">
         <v>546</v>
       </c>
-      <c r="C38" s="145"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="41" t="s">
         <v>205</v>
       </c>
@@ -8210,11 +7993,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="145" t="s">
+      <c r="C39" s="151" t="s">
         <v>59</v>
       </c>
       <c r="D39" s="42" t="s">
@@ -8228,11 +8011,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="109.95" customHeight="1">
-      <c r="A40" s="151"/>
+      <c r="A40" s="146"/>
       <c r="B40" s="30" t="s">
         <v>548</v>
       </c>
-      <c r="C40" s="145"/>
+      <c r="C40" s="151"/>
       <c r="D40" s="41" t="s">
         <v>208</v>
       </c>
@@ -8247,11 +8030,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A41" s="151"/>
+      <c r="A41" s="146"/>
       <c r="B41" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="145"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="45" t="s">
         <v>207</v>
       </c>
@@ -8261,11 +8044,11 @@
       <c r="F41" s="25"/>
     </row>
     <row r="42" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A42" s="151"/>
+      <c r="A42" s="146"/>
       <c r="B42" s="30" t="s">
         <v>549</v>
       </c>
-      <c r="C42" s="145"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="42" t="s">
         <v>209</v>
       </c>
@@ -8275,11 +8058,11 @@
       <c r="F42" s="25"/>
     </row>
     <row r="43" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A43" s="151"/>
+      <c r="A43" s="146"/>
       <c r="B43" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="145"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="41" t="s">
         <v>210</v>
       </c>
@@ -8291,11 +8074,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A44" s="151"/>
+      <c r="A44" s="146"/>
       <c r="B44" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="145"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="42" t="s">
         <v>211</v>
       </c>
@@ -8305,11 +8088,11 @@
       <c r="F44" s="25"/>
     </row>
     <row r="45" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A45" s="151"/>
+      <c r="A45" s="146"/>
       <c r="B45" s="30" t="s">
         <v>550</v>
       </c>
-      <c r="C45" s="145"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="41" t="s">
         <v>212</v>
       </c>
@@ -8321,11 +8104,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A46" s="151"/>
+      <c r="A46" s="146"/>
       <c r="B46" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="145"/>
+      <c r="C46" s="151"/>
       <c r="D46" s="45" t="s">
         <v>213</v>
       </c>
@@ -8335,11 +8118,11 @@
       <c r="F46" s="25"/>
     </row>
     <row r="47" spans="1:7" ht="60" customHeight="1">
-      <c r="A47" s="151"/>
+      <c r="A47" s="146"/>
       <c r="B47" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="145"/>
+      <c r="C47" s="151"/>
       <c r="D47" s="46" t="s">
         <v>214</v>
       </c>
@@ -8351,11 +8134,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A48" s="151"/>
+      <c r="A48" s="146"/>
       <c r="B48" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="145"/>
+      <c r="C48" s="151"/>
       <c r="D48" s="45" t="s">
         <v>215</v>
       </c>
@@ -8365,11 +8148,11 @@
       <c r="F48" s="25"/>
     </row>
     <row r="49" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A49" s="151"/>
+      <c r="A49" s="146"/>
       <c r="B49" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="145"/>
+      <c r="C49" s="151"/>
       <c r="D49" s="46" t="s">
         <v>216</v>
       </c>
@@ -8381,11 +8164,11 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A50" s="151"/>
+      <c r="A50" s="146"/>
       <c r="B50" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C50" s="145"/>
+      <c r="C50" s="151"/>
       <c r="D50" s="42" t="s">
         <v>218</v>
       </c>
@@ -8400,11 +8183,11 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="100.2" customHeight="1">
-      <c r="A51" s="151"/>
+      <c r="A51" s="146"/>
       <c r="B51" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="145"/>
+      <c r="C51" s="151"/>
       <c r="D51" s="41" t="s">
         <v>219</v>
       </c>
@@ -8416,11 +8199,11 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A52" s="151"/>
+      <c r="A52" s="146"/>
       <c r="B52" s="30" t="s">
         <v>552</v>
       </c>
-      <c r="C52" s="145" t="s">
+      <c r="C52" s="151" t="s">
         <v>74</v>
       </c>
       <c r="D52" s="42" t="s">
@@ -8434,11 +8217,11 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A53" s="151"/>
+      <c r="A53" s="146"/>
       <c r="B53" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="145"/>
+      <c r="C53" s="151"/>
       <c r="D53" s="41" t="s">
         <v>221</v>
       </c>
@@ -8450,11 +8233,11 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A54" s="151"/>
+      <c r="A54" s="146"/>
       <c r="B54" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="145"/>
+      <c r="C54" s="151"/>
       <c r="D54" s="41" t="s">
         <v>222</v>
       </c>
@@ -8466,11 +8249,11 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="60" customHeight="1">
-      <c r="A55" s="151"/>
+      <c r="A55" s="146"/>
       <c r="B55" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="145"/>
+      <c r="C55" s="151"/>
       <c r="D55" s="41" t="s">
         <v>223</v>
       </c>
@@ -8482,11 +8265,11 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A56" s="151"/>
+      <c r="A56" s="146"/>
       <c r="B56" s="30" t="s">
         <v>553</v>
       </c>
-      <c r="C56" s="145"/>
+      <c r="C56" s="151"/>
       <c r="D56" s="42" t="s">
         <v>224</v>
       </c>
@@ -8498,11 +8281,11 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A57" s="151"/>
+      <c r="A57" s="146"/>
       <c r="B57" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C57" s="145"/>
+      <c r="C57" s="151"/>
       <c r="D57" s="41" t="s">
         <v>225</v>
       </c>
@@ -8514,11 +8297,11 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A58" s="151"/>
+      <c r="A58" s="146"/>
       <c r="B58" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="145"/>
+      <c r="C58" s="151"/>
       <c r="D58" s="42" t="s">
         <v>226</v>
       </c>
@@ -8530,11 +8313,11 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A59" s="151"/>
+      <c r="A59" s="146"/>
       <c r="B59" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="145"/>
+      <c r="C59" s="151"/>
       <c r="D59" s="41" t="s">
         <v>227</v>
       </c>
@@ -8546,11 +8329,11 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A60" s="151"/>
+      <c r="A60" s="146"/>
       <c r="B60" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C60" s="145"/>
+      <c r="C60" s="151"/>
       <c r="D60" s="42" t="s">
         <v>228</v>
       </c>
@@ -8562,11 +8345,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A61" s="151"/>
+      <c r="A61" s="146"/>
       <c r="B61" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="145"/>
+      <c r="C61" s="151"/>
       <c r="D61" s="41" t="s">
         <v>229</v>
       </c>
@@ -8578,11 +8361,11 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A62" s="151"/>
+      <c r="A62" s="146"/>
       <c r="B62" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="145" t="s">
+      <c r="C62" s="151" t="s">
         <v>325</v>
       </c>
       <c r="D62" s="41" t="s">
@@ -8596,9 +8379,9 @@
       </c>
     </row>
     <row r="63" spans="1:7" ht="34.799999999999997">
-      <c r="A63" s="151"/>
+      <c r="A63" s="146"/>
       <c r="B63" s="30"/>
-      <c r="C63" s="145"/>
+      <c r="C63" s="151"/>
       <c r="D63" s="41" t="s">
         <v>326</v>
       </c>
@@ -8606,11 +8389,11 @@
       <c r="F63" s="25"/>
     </row>
     <row r="64" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A64" s="151"/>
+      <c r="A64" s="146"/>
       <c r="B64" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C64" s="145"/>
+      <c r="C64" s="151"/>
       <c r="D64" s="41" t="s">
         <v>327</v>
       </c>
@@ -8622,11 +8405,11 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A65" s="151"/>
+      <c r="A65" s="146"/>
       <c r="B65" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="145"/>
+      <c r="C65" s="151"/>
       <c r="D65" s="41" t="s">
         <v>230</v>
       </c>
@@ -8638,11 +8421,11 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A66" s="151"/>
+      <c r="A66" s="146"/>
       <c r="B66" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="145"/>
+      <c r="C66" s="151"/>
       <c r="D66" s="41" t="s">
         <v>328</v>
       </c>
@@ -8654,11 +8437,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A67" s="151"/>
+      <c r="A67" s="146"/>
       <c r="B67" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="145"/>
+      <c r="C67" s="151"/>
       <c r="D67" s="41" t="s">
         <v>231</v>
       </c>
@@ -8670,11 +8453,11 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="20.399999999999999">
-      <c r="A68" s="151"/>
+      <c r="A68" s="146"/>
       <c r="B68" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="C68" s="146"/>
+      <c r="C68" s="152"/>
       <c r="D68" s="47" t="s">
         <v>329</v>
       </c>
@@ -8686,11 +8469,11 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A69" s="151"/>
+      <c r="A69" s="146"/>
       <c r="B69" s="30" t="s">
         <v>551</v>
       </c>
-      <c r="C69" s="145" t="s">
+      <c r="C69" s="151" t="s">
         <v>90</v>
       </c>
       <c r="D69" s="41" t="s">
@@ -8704,11 +8487,11 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A70" s="151"/>
+      <c r="A70" s="146"/>
       <c r="B70" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="C70" s="145"/>
+      <c r="C70" s="151"/>
       <c r="D70" s="41" t="s">
         <v>237</v>
       </c>
@@ -8720,11 +8503,11 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A71" s="151"/>
+      <c r="A71" s="146"/>
       <c r="B71" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C71" s="145"/>
+      <c r="C71" s="151"/>
       <c r="D71" s="41" t="s">
         <v>239</v>
       </c>
@@ -8736,11 +8519,11 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A72" s="151"/>
+      <c r="A72" s="146"/>
       <c r="B72" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C72" s="145"/>
+      <c r="C72" s="151"/>
       <c r="D72" s="41" t="s">
         <v>238</v>
       </c>
@@ -8752,11 +8535,11 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A73" s="151"/>
+      <c r="A73" s="146"/>
       <c r="B73" s="30" t="s">
         <v>554</v>
       </c>
-      <c r="C73" s="147" t="s">
+      <c r="C73" s="153" t="s">
         <v>92</v>
       </c>
       <c r="D73" s="42" t="s">
@@ -8770,11 +8553,11 @@
       </c>
     </row>
     <row r="74" spans="1:6" s="21" customFormat="1" ht="40.200000000000003" customHeight="1">
-      <c r="A74" s="151"/>
+      <c r="A74" s="146"/>
       <c r="B74" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="C74" s="147"/>
+      <c r="C74" s="153"/>
       <c r="D74" s="41" t="s">
         <v>241</v>
       </c>
@@ -8786,11 +8569,11 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A75" s="151"/>
+      <c r="A75" s="146"/>
       <c r="B75" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C75" s="147"/>
+      <c r="C75" s="153"/>
       <c r="D75" s="42" t="s">
         <v>242</v>
       </c>
@@ -8802,11 +8585,11 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A76" s="151"/>
+      <c r="A76" s="146"/>
       <c r="B76" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C76" s="147"/>
+      <c r="C76" s="153"/>
       <c r="D76" s="41" t="s">
         <v>243</v>
       </c>
@@ -8818,11 +8601,11 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A77" s="151"/>
+      <c r="A77" s="146"/>
       <c r="B77" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C77" s="147"/>
+      <c r="C77" s="153"/>
       <c r="D77" s="41" t="s">
         <v>244</v>
       </c>
@@ -8834,11 +8617,11 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="20.399999999999999">
-      <c r="A78" s="151"/>
+      <c r="A78" s="146"/>
       <c r="B78" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="C78" s="148" t="s">
+      <c r="C78" s="143" t="s">
         <v>516</v>
       </c>
       <c r="D78" s="69" t="s">
@@ -8852,11 +8635,11 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="52.2">
-      <c r="A79" s="151"/>
+      <c r="A79" s="146"/>
       <c r="B79" s="30" t="s">
         <v>555</v>
       </c>
-      <c r="C79" s="149"/>
+      <c r="C79" s="144"/>
       <c r="D79" s="74" t="s">
         <v>519</v>
       </c>
@@ -8869,6 +8652,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="C73:C77"/>
     <mergeCell ref="C78:C79"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:B2"/>
@@ -8885,8 +8670,6 @@
     <mergeCell ref="C39:C51"/>
     <mergeCell ref="C52:C61"/>
     <mergeCell ref="C62:C68"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="C73:C77"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8909,27 +8692,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="120"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
       <c r="G1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
@@ -8958,43 +8741,43 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="69.599999999999994">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="154" t="s">
         <v>522</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>524</v>
       </c>
-      <c r="C4" s="152" t="s">
+      <c r="C4" s="147" t="s">
         <v>523</v>
       </c>
       <c r="D4" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="153" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="159" t="s">
+      <c r="E4" s="148" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="157" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A5" s="157"/>
+      <c r="A5" s="155"/>
       <c r="B5" s="30" t="s">
         <v>525</v>
       </c>
-      <c r="C5" s="152"/>
+      <c r="C5" s="147"/>
       <c r="D5" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="E5" s="153"/>
-      <c r="F5" s="159"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="157"/>
     </row>
     <row r="6" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A6" s="157"/>
+      <c r="A6" s="155"/>
       <c r="B6" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="152"/>
+      <c r="C6" s="147"/>
       <c r="D6" s="43" t="s">
         <v>412</v>
       </c>
@@ -9009,11 +8792,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="34.799999999999997">
-      <c r="A7" s="157"/>
+      <c r="A7" s="155"/>
       <c r="B7" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="152"/>
+      <c r="C7" s="147"/>
       <c r="D7" s="44" t="s">
         <v>413</v>
       </c>
@@ -9026,11 +8809,11 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A8" s="157"/>
+      <c r="A8" s="155"/>
       <c r="B8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="152"/>
+      <c r="C8" s="147"/>
       <c r="D8" s="42" t="s">
         <v>174</v>
       </c>
@@ -9042,11 +8825,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="104.4">
-      <c r="A9" s="157"/>
+      <c r="A9" s="155"/>
       <c r="B9" s="30" t="s">
         <v>526</v>
       </c>
-      <c r="C9" s="152"/>
+      <c r="C9" s="147"/>
       <c r="D9" s="41" t="s">
         <v>305</v>
       </c>
@@ -9058,11 +8841,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A10" s="157"/>
+      <c r="A10" s="155"/>
       <c r="B10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="150" t="s">
         <v>184</v>
       </c>
       <c r="D10" s="42" t="s">
@@ -9076,11 +8859,11 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A11" s="157"/>
+      <c r="A11" s="155"/>
       <c r="B11" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="155"/>
+      <c r="C11" s="150"/>
       <c r="D11" s="41" t="s">
         <v>179</v>
       </c>
@@ -9092,11 +8875,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="60" customHeight="1">
-      <c r="A12" s="157"/>
+      <c r="A12" s="155"/>
       <c r="B12" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="155"/>
+      <c r="C12" s="150"/>
       <c r="D12" s="41" t="s">
         <v>185</v>
       </c>
@@ -9108,11 +8891,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A13" s="157"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="155"/>
+      <c r="C13" s="150"/>
       <c r="D13" s="41" t="s">
         <v>187</v>
       </c>
@@ -9124,11 +8907,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A14" s="157"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="155"/>
+      <c r="C14" s="150"/>
       <c r="D14" s="42" t="s">
         <v>188</v>
       </c>
@@ -9140,11 +8923,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="52.2">
-      <c r="A15" s="157"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="155"/>
+      <c r="C15" s="150"/>
       <c r="D15" s="41" t="s">
         <v>186</v>
       </c>
@@ -9156,11 +8939,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="55.2" customHeight="1">
-      <c r="A16" s="157"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="155"/>
+      <c r="C16" s="150"/>
       <c r="D16" s="41" t="s">
         <v>189</v>
       </c>
@@ -9172,11 +8955,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="45" customHeight="1">
-      <c r="A17" s="157"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="155"/>
+      <c r="C17" s="150"/>
       <c r="D17" s="41" t="s">
         <v>190</v>
       </c>
@@ -9188,11 +8971,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A18" s="157"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="155"/>
+      <c r="C18" s="150"/>
       <c r="D18" s="41" t="s">
         <v>191</v>
       </c>
@@ -9204,11 +8987,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="60" customHeight="1">
-      <c r="A19" s="157"/>
+      <c r="A19" s="155"/>
       <c r="B19" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="155"/>
+      <c r="C19" s="150"/>
       <c r="D19" s="41" t="s">
         <v>192</v>
       </c>
@@ -9220,11 +9003,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="60" customHeight="1">
-      <c r="A20" s="157"/>
+      <c r="A20" s="155"/>
       <c r="B20" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="155"/>
+      <c r="C20" s="150"/>
       <c r="D20" s="41" t="s">
         <v>193</v>
       </c>
@@ -9236,11 +9019,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="45" customHeight="1">
-      <c r="A21" s="157"/>
+      <c r="A21" s="155"/>
       <c r="B21" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="155"/>
+      <c r="C21" s="150"/>
       <c r="D21" s="41" t="s">
         <v>194</v>
       </c>
@@ -9252,11 +9035,11 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="45" customHeight="1">
-      <c r="A22" s="157"/>
+      <c r="A22" s="155"/>
       <c r="B22" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="155"/>
+      <c r="C22" s="150"/>
       <c r="D22" s="41" t="s">
         <v>195</v>
       </c>
@@ -9268,11 +9051,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="90" customHeight="1">
-      <c r="A23" s="157"/>
+      <c r="A23" s="155"/>
       <c r="B23" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="155" t="s">
+      <c r="C23" s="150" t="s">
         <v>196</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -9289,11 +9072,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A24" s="157"/>
+      <c r="A24" s="155"/>
       <c r="B24" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="155"/>
+      <c r="C24" s="150"/>
       <c r="D24" s="41" t="s">
         <v>199</v>
       </c>
@@ -9305,11 +9088,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="42" customHeight="1">
-      <c r="A25" s="157"/>
+      <c r="A25" s="155"/>
       <c r="B25" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="155"/>
+      <c r="C25" s="150"/>
       <c r="D25" s="41" t="s">
         <v>200</v>
       </c>
@@ -9321,11 +9104,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A26" s="157"/>
+      <c r="A26" s="155"/>
       <c r="B26" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="145" t="s">
+      <c r="C26" s="151" t="s">
         <v>49</v>
       </c>
       <c r="D26" s="41" t="s">
@@ -9339,11 +9122,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="43.2" customHeight="1">
-      <c r="A27" s="157"/>
+      <c r="A27" s="155"/>
       <c r="B27" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="145"/>
+      <c r="C27" s="151"/>
       <c r="D27" s="41" t="s">
         <v>202</v>
       </c>
@@ -9355,11 +9138,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="60" customHeight="1">
-      <c r="A28" s="157"/>
+      <c r="A28" s="155"/>
       <c r="B28" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="145" t="s">
+      <c r="C28" s="151" t="s">
         <v>52</v>
       </c>
       <c r="D28" s="41" t="s">
@@ -9373,11 +9156,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="104.4">
-      <c r="A29" s="157"/>
+      <c r="A29" s="155"/>
       <c r="B29" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="145"/>
+      <c r="C29" s="151"/>
       <c r="D29" s="41" t="s">
         <v>332</v>
       </c>
@@ -9389,11 +9172,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="87">
-      <c r="A30" s="157"/>
+      <c r="A30" s="155"/>
       <c r="B30" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="145"/>
+      <c r="C30" s="151"/>
       <c r="D30" s="41" t="s">
         <v>331</v>
       </c>
@@ -9405,11 +9188,11 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A31" s="157"/>
+      <c r="A31" s="155"/>
       <c r="B31" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="145"/>
+      <c r="C31" s="151"/>
       <c r="D31" s="42" t="s">
         <v>204</v>
       </c>
@@ -9419,11 +9202,11 @@
       <c r="F31" s="38"/>
     </row>
     <row r="32" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A32" s="157"/>
+      <c r="A32" s="155"/>
       <c r="B32" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="145"/>
+      <c r="C32" s="151"/>
       <c r="D32" s="41" t="s">
         <v>205</v>
       </c>
@@ -9435,11 +9218,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A33" s="157"/>
+      <c r="A33" s="155"/>
       <c r="B33" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="145" t="s">
+      <c r="C33" s="151" t="s">
         <v>59</v>
       </c>
       <c r="D33" s="42" t="s">
@@ -9453,11 +9236,11 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="109.95" customHeight="1">
-      <c r="A34" s="157"/>
+      <c r="A34" s="155"/>
       <c r="B34" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="145"/>
+      <c r="C34" s="151"/>
       <c r="D34" s="41" t="s">
         <v>208</v>
       </c>
@@ -9472,11 +9255,11 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A35" s="157"/>
+      <c r="A35" s="155"/>
       <c r="B35" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="145"/>
+      <c r="C35" s="151"/>
       <c r="D35" s="45" t="s">
         <v>207</v>
       </c>
@@ -9488,11 +9271,11 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A36" s="157"/>
+      <c r="A36" s="155"/>
       <c r="B36" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="145"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="42" t="s">
         <v>209</v>
       </c>
@@ -9504,11 +9287,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A37" s="157"/>
+      <c r="A37" s="155"/>
       <c r="B37" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="145"/>
+      <c r="C37" s="151"/>
       <c r="D37" s="41" t="s">
         <v>210</v>
       </c>
@@ -9520,11 +9303,11 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A38" s="157"/>
+      <c r="A38" s="155"/>
       <c r="B38" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="145"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="42" t="s">
         <v>211</v>
       </c>
@@ -9536,11 +9319,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A39" s="157"/>
+      <c r="A39" s="155"/>
       <c r="B39" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="145"/>
+      <c r="C39" s="151"/>
       <c r="D39" s="41" t="s">
         <v>212</v>
       </c>
@@ -9552,11 +9335,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A40" s="157"/>
+      <c r="A40" s="155"/>
       <c r="B40" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="145"/>
+      <c r="C40" s="151"/>
       <c r="D40" s="45" t="s">
         <v>213</v>
       </c>
@@ -9568,11 +9351,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="60" customHeight="1">
-      <c r="A41" s="157"/>
+      <c r="A41" s="155"/>
       <c r="B41" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="145"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="46" t="s">
         <v>214</v>
       </c>
@@ -9584,11 +9367,11 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A42" s="157"/>
+      <c r="A42" s="155"/>
       <c r="B42" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="145"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="45" t="s">
         <v>215</v>
       </c>
@@ -9600,11 +9383,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A43" s="157"/>
+      <c r="A43" s="155"/>
       <c r="B43" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="145"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="46" t="s">
         <v>216</v>
       </c>
@@ -9616,11 +9399,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A44" s="157"/>
+      <c r="A44" s="155"/>
       <c r="B44" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="145"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="42" t="s">
         <v>218</v>
       </c>
@@ -9635,11 +9418,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.2" customHeight="1">
-      <c r="A45" s="157"/>
+      <c r="A45" s="155"/>
       <c r="B45" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="145"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="41" t="s">
         <v>219</v>
       </c>
@@ -9651,11 +9434,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A46" s="157"/>
+      <c r="A46" s="155"/>
       <c r="B46" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="145" t="s">
+      <c r="C46" s="151" t="s">
         <v>74</v>
       </c>
       <c r="D46" s="42" t="s">
@@ -9669,11 +9452,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A47" s="157"/>
+      <c r="A47" s="155"/>
       <c r="B47" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="145"/>
+      <c r="C47" s="151"/>
       <c r="D47" s="41" t="s">
         <v>221</v>
       </c>
@@ -9685,11 +9468,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A48" s="157"/>
+      <c r="A48" s="155"/>
       <c r="B48" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C48" s="145"/>
+      <c r="C48" s="151"/>
       <c r="D48" s="41" t="s">
         <v>222</v>
       </c>
@@ -9701,11 +9484,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="60" customHeight="1">
-      <c r="A49" s="157"/>
+      <c r="A49" s="155"/>
       <c r="B49" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="145"/>
+      <c r="C49" s="151"/>
       <c r="D49" s="41" t="s">
         <v>223</v>
       </c>
@@ -9717,11 +9500,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A50" s="157"/>
+      <c r="A50" s="155"/>
       <c r="B50" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="145"/>
+      <c r="C50" s="151"/>
       <c r="D50" s="42" t="s">
         <v>224</v>
       </c>
@@ -9733,11 +9516,11 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A51" s="157"/>
+      <c r="A51" s="155"/>
       <c r="B51" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="145"/>
+      <c r="C51" s="151"/>
       <c r="D51" s="41" t="s">
         <v>225</v>
       </c>
@@ -9749,11 +9532,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A52" s="157"/>
+      <c r="A52" s="155"/>
       <c r="B52" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="145"/>
+      <c r="C52" s="151"/>
       <c r="D52" s="42" t="s">
         <v>226</v>
       </c>
@@ -9765,11 +9548,11 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A53" s="157"/>
+      <c r="A53" s="155"/>
       <c r="B53" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="145"/>
+      <c r="C53" s="151"/>
       <c r="D53" s="41" t="s">
         <v>227</v>
       </c>
@@ -9781,11 +9564,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A54" s="157"/>
+      <c r="A54" s="155"/>
       <c r="B54" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="145"/>
+      <c r="C54" s="151"/>
       <c r="D54" s="42" t="s">
         <v>228</v>
       </c>
@@ -9797,11 +9580,11 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A55" s="157"/>
+      <c r="A55" s="155"/>
       <c r="B55" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="145"/>
+      <c r="C55" s="151"/>
       <c r="D55" s="41" t="s">
         <v>229</v>
       </c>
@@ -9813,11 +9596,11 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A56" s="157"/>
+      <c r="A56" s="155"/>
       <c r="B56" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="145" t="s">
+      <c r="C56" s="151" t="s">
         <v>325</v>
       </c>
       <c r="D56" s="41" t="s">
@@ -9831,11 +9614,11 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A57" s="157"/>
+      <c r="A57" s="155"/>
       <c r="B57" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C57" s="145"/>
+      <c r="C57" s="151"/>
       <c r="D57" s="41" t="s">
         <v>327</v>
       </c>
@@ -9847,11 +9630,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A58" s="157"/>
+      <c r="A58" s="155"/>
       <c r="B58" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="145"/>
+      <c r="C58" s="151"/>
       <c r="D58" s="41" t="s">
         <v>230</v>
       </c>
@@ -9863,11 +9646,11 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A59" s="157"/>
+      <c r="A59" s="155"/>
       <c r="B59" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="145"/>
+      <c r="C59" s="151"/>
       <c r="D59" s="41" t="s">
         <v>328</v>
       </c>
@@ -9879,11 +9662,11 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A60" s="157"/>
+      <c r="A60" s="155"/>
       <c r="B60" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="145"/>
+      <c r="C60" s="151"/>
       <c r="D60" s="41" t="s">
         <v>231</v>
       </c>
@@ -9895,11 +9678,11 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="20.399999999999999">
-      <c r="A61" s="157"/>
+      <c r="A61" s="155"/>
       <c r="B61" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="C61" s="146"/>
+      <c r="C61" s="152"/>
       <c r="D61" s="47" t="s">
         <v>329</v>
       </c>
@@ -9911,11 +9694,11 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A62" s="157"/>
+      <c r="A62" s="155"/>
       <c r="B62" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="145" t="s">
+      <c r="C62" s="151" t="s">
         <v>90</v>
       </c>
       <c r="D62" s="41" t="s">
@@ -9929,11 +9712,11 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A63" s="157"/>
+      <c r="A63" s="155"/>
       <c r="B63" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="C63" s="145"/>
+      <c r="C63" s="151"/>
       <c r="D63" s="41" t="s">
         <v>237</v>
       </c>
@@ -9945,11 +9728,11 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A64" s="157"/>
+      <c r="A64" s="155"/>
       <c r="B64" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C64" s="145"/>
+      <c r="C64" s="151"/>
       <c r="D64" s="41" t="s">
         <v>239</v>
       </c>
@@ -9961,11 +9744,11 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A65" s="157"/>
+      <c r="A65" s="155"/>
       <c r="B65" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="C65" s="145"/>
+      <c r="C65" s="151"/>
       <c r="D65" s="41" t="s">
         <v>238</v>
       </c>
@@ -9977,11 +9760,11 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A66" s="157"/>
+      <c r="A66" s="155"/>
       <c r="B66" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="147" t="s">
+      <c r="C66" s="153" t="s">
         <v>92</v>
       </c>
       <c r="D66" s="42" t="s">
@@ -9995,11 +9778,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="21" customFormat="1" ht="40.200000000000003" customHeight="1">
-      <c r="A67" s="157"/>
+      <c r="A67" s="155"/>
       <c r="B67" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="C67" s="147"/>
+      <c r="C67" s="153"/>
       <c r="D67" s="41" t="s">
         <v>241</v>
       </c>
@@ -10011,11 +9794,11 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A68" s="157"/>
+      <c r="A68" s="155"/>
       <c r="B68" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C68" s="147"/>
+      <c r="C68" s="153"/>
       <c r="D68" s="42" t="s">
         <v>242</v>
       </c>
@@ -10027,11 +9810,11 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A69" s="157"/>
+      <c r="A69" s="155"/>
       <c r="B69" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C69" s="147"/>
+      <c r="C69" s="153"/>
       <c r="D69" s="41" t="s">
         <v>243</v>
       </c>
@@ -10043,11 +9826,11 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A70" s="157"/>
+      <c r="A70" s="155"/>
       <c r="B70" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C70" s="147"/>
+      <c r="C70" s="153"/>
       <c r="D70" s="41" t="s">
         <v>244</v>
       </c>
@@ -10059,11 +9842,11 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="20.399999999999999">
-      <c r="A71" s="157"/>
+      <c r="A71" s="155"/>
       <c r="B71" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="C71" s="148" t="s">
+      <c r="C71" s="143" t="s">
         <v>516</v>
       </c>
       <c r="D71" s="69" t="s">
@@ -10077,11 +9860,11 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="52.2">
-      <c r="A72" s="158"/>
+      <c r="A72" s="156"/>
       <c r="B72" s="30" t="s">
         <v>527</v>
       </c>
-      <c r="C72" s="149"/>
+      <c r="C72" s="144"/>
       <c r="D72" s="74" t="s">
         <v>519</v>
       </c>
@@ -10094,6 +9877,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C46:C55"/>
     <mergeCell ref="C56:C61"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="C66:C70"/>
@@ -10110,7 +9894,6 @@
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C28:C32"/>
     <mergeCell ref="C33:C45"/>
-    <mergeCell ref="C46:C55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10133,27 +9916,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="120"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
       <c r="G1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
@@ -10182,13 +9965,13 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="104.4">
-      <c r="A4" s="160" t="s">
+      <c r="A4" s="158" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="165" t="s">
+      <c r="C4" s="159" t="s">
         <v>98</v>
       </c>
       <c r="D4" s="48" t="s">
@@ -10202,11 +9985,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="120" customHeight="1">
-      <c r="A5" s="160"/>
+      <c r="A5" s="158"/>
       <c r="B5" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="165"/>
+      <c r="C5" s="159"/>
       <c r="D5" s="48" t="s">
         <v>335</v>
       </c>
@@ -10219,11 +10002,11 @@
       <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" ht="121.8">
-      <c r="A6" s="160"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="165"/>
+      <c r="C6" s="159"/>
       <c r="D6" s="48" t="s">
         <v>336</v>
       </c>
@@ -10236,7 +10019,7 @@
       <c r="G6" s="24"/>
     </row>
     <row r="7" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A7" s="160"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="30" t="s">
         <v>102</v>
       </c>
@@ -10254,11 +10037,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="109.95" customHeight="1">
-      <c r="A8" s="160"/>
+      <c r="A8" s="158"/>
       <c r="B8" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="173" t="s">
+      <c r="C8" s="160" t="s">
         <v>249</v>
       </c>
       <c r="D8" s="48" t="s">
@@ -10275,11 +10058,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A9" s="160"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="173"/>
+      <c r="C9" s="160"/>
       <c r="D9" s="48" t="s">
         <v>251</v>
       </c>
@@ -10291,11 +10074,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A10" s="160"/>
+      <c r="A10" s="158"/>
       <c r="B10" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="173"/>
+      <c r="C10" s="160"/>
       <c r="D10" s="48" t="s">
         <v>252</v>
       </c>
@@ -10307,11 +10090,11 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A11" s="160"/>
+      <c r="A11" s="158"/>
       <c r="B11" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="161" t="s">
         <v>108</v>
       </c>
       <c r="D11" s="48" t="s">
@@ -10325,11 +10108,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A12" s="160"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="162"/>
       <c r="D12" s="47" t="s">
         <v>324</v>
       </c>
@@ -10344,11 +10127,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="115.5" customHeight="1">
-      <c r="A13" s="160"/>
+      <c r="A13" s="158"/>
       <c r="B13" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="102"/>
+      <c r="C13" s="162"/>
       <c r="D13" s="48" t="s">
         <v>341</v>
       </c>
@@ -10360,11 +10143,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A14" s="160"/>
+      <c r="A14" s="158"/>
       <c r="B14" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="102"/>
+      <c r="C14" s="162"/>
       <c r="D14" s="48" t="s">
         <v>257</v>
       </c>
@@ -10376,11 +10159,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="60" customHeight="1">
-      <c r="A15" s="160"/>
+      <c r="A15" s="158"/>
       <c r="B15" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="102"/>
+      <c r="C15" s="162"/>
       <c r="D15" s="48" t="s">
         <v>258</v>
       </c>
@@ -10392,11 +10175,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="90" customHeight="1">
-      <c r="A16" s="160"/>
+      <c r="A16" s="158"/>
       <c r="B16" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="102"/>
+      <c r="C16" s="162"/>
       <c r="D16" s="48" t="s">
         <v>259</v>
       </c>
@@ -10408,11 +10191,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="66" customHeight="1">
-      <c r="A17" s="160"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="102"/>
+      <c r="C17" s="162"/>
       <c r="D17" s="48" t="s">
         <v>312</v>
       </c>
@@ -10427,7 +10210,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="34.799999999999997">
-      <c r="A18" s="160"/>
+      <c r="A18" s="158"/>
       <c r="B18" s="30" t="s">
         <v>118</v>
       </c>
@@ -10445,11 +10228,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="79.5" customHeight="1">
-      <c r="A19" s="160"/>
+      <c r="A19" s="158"/>
       <c r="B19" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="165" t="s">
+      <c r="C19" s="159" t="s">
         <v>121</v>
       </c>
       <c r="D19" s="48" t="s">
@@ -10463,11 +10246,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A20" s="160"/>
+      <c r="A20" s="158"/>
       <c r="B20" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="165"/>
+      <c r="C20" s="159"/>
       <c r="D20" s="48" t="s">
         <v>261</v>
       </c>
@@ -10482,11 +10265,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A21" s="160"/>
+      <c r="A21" s="158"/>
       <c r="B21" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="165"/>
+      <c r="C21" s="159"/>
       <c r="D21" s="48" t="s">
         <v>262</v>
       </c>
@@ -10498,11 +10281,11 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A22" s="160"/>
+      <c r="A22" s="158"/>
       <c r="B22" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="165"/>
+      <c r="C22" s="159"/>
       <c r="D22" s="48" t="s">
         <v>349</v>
       </c>
@@ -10514,13 +10297,13 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A23" s="169" t="s">
+      <c r="A23" s="163" t="s">
         <v>181</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="C23" s="171" t="s">
+      <c r="C23" s="165" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="41" t="s">
@@ -10534,11 +10317,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A24" s="170"/>
+      <c r="A24" s="164"/>
       <c r="B24" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C24" s="145"/>
+      <c r="C24" s="151"/>
       <c r="D24" s="41" t="s">
         <v>268</v>
       </c>
@@ -10550,11 +10333,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A25" s="170"/>
+      <c r="A25" s="164"/>
       <c r="B25" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="C25" s="145"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="41" t="s">
         <v>269</v>
       </c>
@@ -10566,11 +10349,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A26" s="170"/>
+      <c r="A26" s="164"/>
       <c r="B26" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="145"/>
+      <c r="C26" s="151"/>
       <c r="D26" s="42" t="s">
         <v>270</v>
       </c>
@@ -10582,11 +10365,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A27" s="170"/>
+      <c r="A27" s="164"/>
       <c r="B27" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="C27" s="145"/>
+      <c r="C27" s="151"/>
       <c r="D27" s="42" t="s">
         <v>129</v>
       </c>
@@ -10598,11 +10381,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" s="21" customFormat="1" ht="40.200000000000003" customHeight="1">
-      <c r="A28" s="170"/>
+      <c r="A28" s="164"/>
       <c r="B28" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="C28" s="145"/>
+      <c r="C28" s="151"/>
       <c r="D28" s="41" t="s">
         <v>271</v>
       </c>
@@ -10614,11 +10397,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A29" s="170"/>
+      <c r="A29" s="164"/>
       <c r="B29" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="145"/>
+      <c r="C29" s="151"/>
       <c r="D29" s="42" t="s">
         <v>272</v>
       </c>
@@ -10630,11 +10413,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A30" s="170"/>
+      <c r="A30" s="164"/>
       <c r="B30" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="C30" s="145"/>
+      <c r="C30" s="151"/>
       <c r="D30" s="42" t="s">
         <v>273</v>
       </c>
@@ -10646,11 +10429,11 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A31" s="170"/>
+      <c r="A31" s="164"/>
       <c r="B31" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="C31" s="145"/>
+      <c r="C31" s="151"/>
       <c r="D31" s="42" t="s">
         <v>274</v>
       </c>
@@ -10662,11 +10445,11 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A32" s="170"/>
+      <c r="A32" s="164"/>
       <c r="B32" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="C32" s="145"/>
+      <c r="C32" s="151"/>
       <c r="D32" s="42" t="s">
         <v>133</v>
       </c>
@@ -10678,11 +10461,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A33" s="170"/>
+      <c r="A33" s="164"/>
       <c r="B33" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="145"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="41" t="s">
         <v>275</v>
       </c>
@@ -10697,11 +10480,11 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A34" s="170"/>
+      <c r="A34" s="164"/>
       <c r="B34" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="C34" s="145"/>
+      <c r="C34" s="151"/>
       <c r="D34" s="42" t="s">
         <v>277</v>
       </c>
@@ -10711,16 +10494,16 @@
       <c r="F34" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="G34" s="172" t="s">
+      <c r="G34" s="166" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A35" s="170"/>
+      <c r="A35" s="164"/>
       <c r="B35" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="C35" s="145"/>
+      <c r="C35" s="151"/>
       <c r="D35" s="42" t="s">
         <v>278</v>
       </c>
@@ -10730,14 +10513,14 @@
       <c r="F35" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="G35" s="172"/>
+      <c r="G35" s="166"/>
     </row>
     <row r="36" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A36" s="170"/>
+      <c r="A36" s="164"/>
       <c r="B36" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="145"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="42" t="s">
         <v>137</v>
       </c>
@@ -10747,14 +10530,14 @@
       <c r="F36" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="G36" s="172"/>
+      <c r="G36" s="166"/>
     </row>
     <row r="37" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A37" s="170"/>
+      <c r="A37" s="164"/>
       <c r="B37" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="C37" s="145"/>
+      <c r="C37" s="151"/>
       <c r="D37" s="42" t="s">
         <v>390</v>
       </c>
@@ -10764,14 +10547,14 @@
       <c r="F37" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="G37" s="172"/>
+      <c r="G37" s="166"/>
     </row>
     <row r="38" spans="1:7" ht="20.399999999999999">
-      <c r="A38" s="170"/>
+      <c r="A38" s="164"/>
       <c r="B38" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="C38" s="145"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="41" t="s">
         <v>394</v>
       </c>
@@ -10781,14 +10564,14 @@
       <c r="F38" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="G38" s="172"/>
+      <c r="G38" s="166"/>
     </row>
     <row r="39" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A39" s="170"/>
+      <c r="A39" s="164"/>
       <c r="B39" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="C39" s="145"/>
+      <c r="C39" s="151"/>
       <c r="D39" s="41" t="s">
         <v>286</v>
       </c>
@@ -10798,14 +10581,14 @@
       <c r="F39" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="G39" s="172"/>
+      <c r="G39" s="166"/>
     </row>
     <row r="40" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A40" s="170"/>
+      <c r="A40" s="164"/>
       <c r="B40" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="C40" s="145" t="s">
+      <c r="C40" s="151" t="s">
         <v>449</v>
       </c>
       <c r="D40" s="41" t="s">
@@ -10817,14 +10600,14 @@
       <c r="F40" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="G40" s="172"/>
+      <c r="G40" s="166"/>
     </row>
     <row r="41" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A41" s="170"/>
+      <c r="A41" s="164"/>
       <c r="B41" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="C41" s="145"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="41" t="s">
         <v>268</v>
       </c>
@@ -10836,11 +10619,11 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A42" s="170"/>
+      <c r="A42" s="164"/>
       <c r="B42" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="C42" s="145"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="41" t="s">
         <v>280</v>
       </c>
@@ -10852,11 +10635,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A43" s="170"/>
+      <c r="A43" s="164"/>
       <c r="B43" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C43" s="145"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="42" t="s">
         <v>129</v>
       </c>
@@ -10868,11 +10651,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A44" s="170"/>
+      <c r="A44" s="164"/>
       <c r="B44" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="C44" s="145"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="41" t="s">
         <v>281</v>
       </c>
@@ -10884,11 +10667,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A45" s="170"/>
+      <c r="A45" s="164"/>
       <c r="B45" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="C45" s="145"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="42" t="s">
         <v>282</v>
       </c>
@@ -10900,11 +10683,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A46" s="170"/>
+      <c r="A46" s="164"/>
       <c r="B46" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="C46" s="145"/>
+      <c r="C46" s="151"/>
       <c r="D46" s="42" t="s">
         <v>283</v>
       </c>
@@ -10916,11 +10699,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A47" s="170"/>
+      <c r="A47" s="164"/>
       <c r="B47" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="C47" s="145"/>
+      <c r="C47" s="151"/>
       <c r="D47" s="42" t="s">
         <v>284</v>
       </c>
@@ -10932,11 +10715,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A48" s="170"/>
+      <c r="A48" s="164"/>
       <c r="B48" s="30" t="s">
         <v>375</v>
       </c>
-      <c r="C48" s="145"/>
+      <c r="C48" s="151"/>
       <c r="D48" s="41" t="s">
         <v>380</v>
       </c>
@@ -10948,11 +10731,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="20.399999999999999">
-      <c r="A49" s="170"/>
+      <c r="A49" s="164"/>
       <c r="B49" s="30" t="s">
         <v>376</v>
       </c>
-      <c r="C49" s="145"/>
+      <c r="C49" s="151"/>
       <c r="D49" s="41" t="s">
         <v>381</v>
       </c>
@@ -10964,11 +10747,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A50" s="170"/>
+      <c r="A50" s="164"/>
       <c r="B50" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="C50" s="145"/>
+      <c r="C50" s="151"/>
       <c r="D50" s="42" t="s">
         <v>135</v>
       </c>
@@ -10980,11 +10763,11 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A51" s="170"/>
+      <c r="A51" s="164"/>
       <c r="B51" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="C51" s="145"/>
+      <c r="C51" s="151"/>
       <c r="D51" s="42" t="s">
         <v>136</v>
       </c>
@@ -10996,11 +10779,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A52" s="170"/>
+      <c r="A52" s="164"/>
       <c r="B52" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="C52" s="145"/>
+      <c r="C52" s="151"/>
       <c r="D52" s="42" t="s">
         <v>137</v>
       </c>
@@ -11012,11 +10795,11 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A53" s="170"/>
+      <c r="A53" s="164"/>
       <c r="B53" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="C53" s="145"/>
+      <c r="C53" s="151"/>
       <c r="D53" s="41" t="s">
         <v>287</v>
       </c>
@@ -11028,11 +10811,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A54" s="170"/>
+      <c r="A54" s="164"/>
       <c r="B54" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C54" s="171" t="s">
+      <c r="C54" s="165" t="s">
         <v>165</v>
       </c>
       <c r="D54" s="41" t="s">
@@ -11046,11 +10829,11 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A55" s="170"/>
+      <c r="A55" s="164"/>
       <c r="B55" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="C55" s="145"/>
+      <c r="C55" s="151"/>
       <c r="D55" s="41" t="s">
         <v>289</v>
       </c>
@@ -11062,11 +10845,11 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A56" s="170"/>
+      <c r="A56" s="164"/>
       <c r="B56" s="30" t="s">
         <v>383</v>
       </c>
-      <c r="C56" s="145"/>
+      <c r="C56" s="151"/>
       <c r="D56" s="41" t="s">
         <v>290</v>
       </c>
@@ -11078,11 +10861,11 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A57" s="170"/>
+      <c r="A57" s="164"/>
       <c r="B57" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="C57" s="145"/>
+      <c r="C57" s="151"/>
       <c r="D57" s="41" t="s">
         <v>129</v>
       </c>
@@ -11094,11 +10877,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A58" s="170"/>
+      <c r="A58" s="164"/>
       <c r="B58" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="C58" s="145"/>
+      <c r="C58" s="151"/>
       <c r="D58" s="41" t="s">
         <v>141</v>
       </c>
@@ -11110,11 +10893,11 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A59" s="170"/>
+      <c r="A59" s="164"/>
       <c r="B59" s="30" t="s">
         <v>386</v>
       </c>
-      <c r="C59" s="145"/>
+      <c r="C59" s="151"/>
       <c r="D59" s="41" t="s">
         <v>142</v>
       </c>
@@ -11126,11 +10909,11 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A60" s="170"/>
+      <c r="A60" s="164"/>
       <c r="B60" s="30" t="s">
         <v>387</v>
       </c>
-      <c r="C60" s="145"/>
+      <c r="C60" s="151"/>
       <c r="D60" s="41" t="s">
         <v>143</v>
       </c>
@@ -11142,11 +10925,11 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A61" s="170"/>
+      <c r="A61" s="164"/>
       <c r="B61" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="C61" s="145"/>
+      <c r="C61" s="151"/>
       <c r="D61" s="41" t="s">
         <v>144</v>
       </c>
@@ -11158,11 +10941,11 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A62" s="170"/>
+      <c r="A62" s="164"/>
       <c r="B62" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="C62" s="145"/>
+      <c r="C62" s="151"/>
       <c r="D62" s="41" t="s">
         <v>291</v>
       </c>
@@ -11174,11 +10957,11 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A63" s="170"/>
+      <c r="A63" s="164"/>
       <c r="B63" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C63" s="171" t="s">
+      <c r="C63" s="165" t="s">
         <v>166</v>
       </c>
       <c r="D63" s="41" t="s">
@@ -11192,11 +10975,11 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A64" s="170"/>
+      <c r="A64" s="164"/>
       <c r="B64" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="C64" s="171"/>
+      <c r="C64" s="165"/>
       <c r="D64" s="41" t="s">
         <v>268</v>
       </c>
@@ -11208,11 +10991,11 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A65" s="170"/>
+      <c r="A65" s="164"/>
       <c r="B65" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="C65" s="171"/>
+      <c r="C65" s="165"/>
       <c r="D65" s="41" t="s">
         <v>292</v>
       </c>
@@ -11224,11 +11007,11 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A66" s="170"/>
+      <c r="A66" s="164"/>
       <c r="B66" s="30" t="s">
         <v>397</v>
       </c>
-      <c r="C66" s="171"/>
+      <c r="C66" s="165"/>
       <c r="D66" s="42" t="s">
         <v>128</v>
       </c>
@@ -11240,11 +11023,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A67" s="170"/>
+      <c r="A67" s="164"/>
       <c r="B67" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="C67" s="171"/>
+      <c r="C67" s="165"/>
       <c r="D67" s="42" t="s">
         <v>129</v>
       </c>
@@ -11256,11 +11039,11 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A68" s="170"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="C68" s="171"/>
+      <c r="C68" s="165"/>
       <c r="D68" s="42" t="s">
         <v>130</v>
       </c>
@@ -11272,11 +11055,11 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A69" s="170"/>
+      <c r="A69" s="164"/>
       <c r="B69" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="C69" s="171"/>
+      <c r="C69" s="165"/>
       <c r="D69" s="42" t="s">
         <v>131</v>
       </c>
@@ -11288,11 +11071,11 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A70" s="170"/>
+      <c r="A70" s="164"/>
       <c r="B70" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="C70" s="171"/>
+      <c r="C70" s="165"/>
       <c r="D70" s="42" t="s">
         <v>132</v>
       </c>
@@ -11304,11 +11087,11 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A71" s="170"/>
+      <c r="A71" s="164"/>
       <c r="B71" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="C71" s="171"/>
+      <c r="C71" s="165"/>
       <c r="D71" s="42" t="s">
         <v>139</v>
       </c>
@@ -11320,11 +11103,11 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A72" s="170"/>
+      <c r="A72" s="164"/>
       <c r="B72" s="30" t="s">
         <v>403</v>
       </c>
-      <c r="C72" s="171"/>
+      <c r="C72" s="165"/>
       <c r="D72" s="42" t="s">
         <v>140</v>
       </c>
@@ -11336,11 +11119,11 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A73" s="170"/>
+      <c r="A73" s="164"/>
       <c r="B73" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="C73" s="171"/>
+      <c r="C73" s="165"/>
       <c r="D73" s="42" t="s">
         <v>392</v>
       </c>
@@ -11352,11 +11135,11 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A74" s="170"/>
+      <c r="A74" s="164"/>
       <c r="B74" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="C74" s="171"/>
+      <c r="C74" s="165"/>
       <c r="D74" s="42" t="s">
         <v>133</v>
       </c>
@@ -11368,11 +11151,11 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A75" s="170"/>
+      <c r="A75" s="164"/>
       <c r="B75" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="C75" s="171"/>
+      <c r="C75" s="165"/>
       <c r="D75" s="42" t="s">
         <v>134</v>
       </c>
@@ -11384,11 +11167,11 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A76" s="170"/>
+      <c r="A76" s="164"/>
       <c r="B76" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="C76" s="171"/>
+      <c r="C76" s="165"/>
       <c r="D76" s="42" t="s">
         <v>393</v>
       </c>
@@ -11400,11 +11183,11 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A77" s="170"/>
+      <c r="A77" s="164"/>
       <c r="B77" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="C77" s="171"/>
+      <c r="C77" s="165"/>
       <c r="D77" s="42" t="s">
         <v>135</v>
       </c>
@@ -11416,11 +11199,11 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A78" s="170"/>
+      <c r="A78" s="164"/>
       <c r="B78" s="30" t="s">
         <v>409</v>
       </c>
-      <c r="C78" s="171"/>
+      <c r="C78" s="165"/>
       <c r="D78" s="42" t="s">
         <v>136</v>
       </c>
@@ -11432,11 +11215,11 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A79" s="170"/>
+      <c r="A79" s="164"/>
       <c r="B79" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="C79" s="171"/>
+      <c r="C79" s="165"/>
       <c r="D79" s="42" t="s">
         <v>137</v>
       </c>
@@ -11448,11 +11231,11 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A80" s="170"/>
+      <c r="A80" s="164"/>
       <c r="B80" s="30" t="s">
         <v>411</v>
       </c>
-      <c r="C80" s="171"/>
+      <c r="C80" s="165"/>
       <c r="D80" s="42" t="s">
         <v>138</v>
       </c>
@@ -11464,7 +11247,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="66" customHeight="1">
-      <c r="A81" s="162" t="s">
+      <c r="A81" s="168" t="s">
         <v>182</v>
       </c>
       <c r="B81" s="30" t="s">
@@ -11484,7 +11267,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A82" s="163"/>
+      <c r="A82" s="169"/>
       <c r="B82" s="30" t="s">
         <v>505</v>
       </c>
@@ -11502,7 +11285,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A83" s="163"/>
+      <c r="A83" s="169"/>
       <c r="B83" s="30" t="s">
         <v>507</v>
       </c>
@@ -11520,11 +11303,11 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="33" customHeight="1">
-      <c r="A84" s="163"/>
+      <c r="A84" s="169"/>
       <c r="B84" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="C84" s="164"/>
+      <c r="C84" s="121"/>
       <c r="D84" s="41" t="s">
         <v>148</v>
       </c>
@@ -11536,11 +11319,11 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A85" s="163"/>
+      <c r="A85" s="169"/>
       <c r="B85" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="C85" s="106"/>
+      <c r="C85" s="124"/>
       <c r="D85" s="42" t="s">
         <v>149</v>
       </c>
@@ -11568,11 +11351,11 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A87" s="99"/>
+      <c r="A87" s="170"/>
       <c r="B87" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="C87" s="165"/>
+      <c r="C87" s="159"/>
       <c r="D87" s="49" t="s">
         <v>152</v>
       </c>
@@ -11582,11 +11365,11 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A88" s="99"/>
+      <c r="A88" s="170"/>
       <c r="B88" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="C88" s="165"/>
+      <c r="C88" s="159"/>
       <c r="D88" s="49" t="s">
         <v>153</v>
       </c>
@@ -11596,11 +11379,11 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A89" s="99"/>
+      <c r="A89" s="170"/>
       <c r="B89" s="33" t="s">
         <v>422</v>
       </c>
-      <c r="C89" s="165"/>
+      <c r="C89" s="159"/>
       <c r="D89" s="48" t="s">
         <v>154</v>
       </c>
@@ -11610,11 +11393,11 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A90" s="99"/>
+      <c r="A90" s="170"/>
       <c r="B90" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="C90" s="165"/>
+      <c r="C90" s="159"/>
       <c r="D90" s="49" t="s">
         <v>155</v>
       </c>
@@ -11624,11 +11407,11 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A91" s="99"/>
+      <c r="A91" s="170"/>
       <c r="B91" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="C91" s="165"/>
+      <c r="C91" s="159"/>
       <c r="D91" s="49" t="s">
         <v>156</v>
       </c>
@@ -11638,11 +11421,11 @@
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A92" s="99"/>
+      <c r="A92" s="170"/>
       <c r="B92" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="C92" s="165"/>
+      <c r="C92" s="159"/>
       <c r="D92" s="49" t="s">
         <v>157</v>
       </c>
@@ -11652,11 +11435,11 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="60" customHeight="1">
-      <c r="A93" s="99"/>
+      <c r="A93" s="170"/>
       <c r="B93" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="C93" s="165"/>
+      <c r="C93" s="159"/>
       <c r="D93" s="48" t="s">
         <v>298</v>
       </c>
@@ -11666,11 +11449,11 @@
       </c>
     </row>
     <row r="94" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A94" s="99"/>
+      <c r="A94" s="170"/>
       <c r="B94" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="C94" s="165"/>
+      <c r="C94" s="159"/>
       <c r="D94" s="48" t="s">
         <v>300</v>
       </c>
@@ -11680,11 +11463,11 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A95" s="99"/>
+      <c r="A95" s="170"/>
       <c r="B95" s="33" t="s">
         <v>432</v>
       </c>
-      <c r="C95" s="165"/>
+      <c r="C95" s="159"/>
       <c r="D95" s="48" t="s">
         <v>160</v>
       </c>
@@ -11694,11 +11477,11 @@
       </c>
     </row>
     <row r="96" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A96" s="99"/>
+      <c r="A96" s="170"/>
       <c r="B96" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="C96" s="165"/>
+      <c r="C96" s="159"/>
       <c r="D96" s="48" t="s">
         <v>301</v>
       </c>
@@ -11708,11 +11491,11 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A97" s="99"/>
+      <c r="A97" s="170"/>
       <c r="B97" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C97" s="165"/>
+      <c r="C97" s="159"/>
       <c r="D97" s="48" t="s">
         <v>161</v>
       </c>
@@ -11722,11 +11505,11 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A98" s="99"/>
+      <c r="A98" s="170"/>
       <c r="B98" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="C98" s="165"/>
+      <c r="C98" s="159"/>
       <c r="D98" s="48" t="s">
         <v>302</v>
       </c>
@@ -11736,11 +11519,11 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A99" s="99"/>
+      <c r="A99" s="170"/>
       <c r="B99" s="33" t="s">
         <v>436</v>
       </c>
-      <c r="C99" s="165"/>
+      <c r="C99" s="159"/>
       <c r="D99" s="48" t="s">
         <v>303</v>
       </c>
@@ -11750,11 +11533,11 @@
       </c>
     </row>
     <row r="100" spans="1:6" ht="52.2">
-      <c r="A100" s="99"/>
+      <c r="A100" s="170"/>
       <c r="B100" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="C100" s="166" t="s">
+      <c r="C100" s="172" t="s">
         <v>472</v>
       </c>
       <c r="D100" s="48" t="s">
@@ -11766,11 +11549,11 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="20.399999999999999">
-      <c r="A101" s="99"/>
+      <c r="A101" s="170"/>
       <c r="B101" s="33" t="s">
         <v>476</v>
       </c>
-      <c r="C101" s="167"/>
+      <c r="C101" s="173"/>
       <c r="D101" s="48" t="s">
         <v>473</v>
       </c>
@@ -11780,11 +11563,11 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="34.799999999999997">
-      <c r="A102" s="99"/>
+      <c r="A102" s="170"/>
       <c r="B102" s="33" t="s">
         <v>477</v>
       </c>
-      <c r="C102" s="167"/>
+      <c r="C102" s="173"/>
       <c r="D102" s="48" t="s">
         <v>480</v>
       </c>
@@ -11794,11 +11577,11 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="20.399999999999999">
-      <c r="A103" s="100"/>
+      <c r="A103" s="171"/>
       <c r="B103" s="33" t="s">
         <v>479</v>
       </c>
-      <c r="C103" s="168"/>
+      <c r="C103" s="174"/>
       <c r="D103" s="48" t="s">
         <v>474</v>
       </c>
@@ -11808,7 +11591,7 @@
       </c>
     </row>
     <row r="104" spans="1:6" ht="52.2">
-      <c r="A104" s="160" t="s">
+      <c r="A104" s="158" t="s">
         <v>469</v>
       </c>
       <c r="B104" s="32" t="s">
@@ -11826,7 +11609,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A105" s="160"/>
+      <c r="A105" s="158"/>
       <c r="B105" s="32" t="s">
         <v>437</v>
       </c>
@@ -11842,7 +11625,7 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="126" customHeight="1">
-      <c r="A106" s="160"/>
+      <c r="A106" s="158"/>
       <c r="B106" s="32" t="s">
         <v>438</v>
       </c>
@@ -11858,7 +11641,7 @@
       </c>
     </row>
     <row r="107" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A107" s="160"/>
+      <c r="A107" s="158"/>
       <c r="B107" s="32" t="s">
         <v>439</v>
       </c>
@@ -11874,7 +11657,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" ht="156.6">
-      <c r="A108" s="108"/>
+      <c r="A108" s="110"/>
       <c r="B108" s="53" t="s">
         <v>465</v>
       </c>
@@ -11892,7 +11675,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" ht="34.799999999999997">
-      <c r="A109" s="161"/>
+      <c r="A109" s="167"/>
       <c r="B109" s="53" t="s">
         <v>457</v>
       </c>
@@ -11911,6 +11694,20 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A104:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A81:A85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="A87:A103"/>
+    <mergeCell ref="C87:C92"/>
+    <mergeCell ref="C93:C99"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="A23:A80"/>
+    <mergeCell ref="C23:C39"/>
+    <mergeCell ref="G34:G40"/>
+    <mergeCell ref="C40:C53"/>
+    <mergeCell ref="C54:C62"/>
+    <mergeCell ref="C63:C80"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -11919,20 +11716,6 @@
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="C11:C17"/>
     <mergeCell ref="C19:C22"/>
-    <mergeCell ref="A23:A80"/>
-    <mergeCell ref="C23:C39"/>
-    <mergeCell ref="G34:G40"/>
-    <mergeCell ref="C40:C53"/>
-    <mergeCell ref="C54:C62"/>
-    <mergeCell ref="C63:C80"/>
-    <mergeCell ref="A104:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A81:A85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="A87:A103"/>
-    <mergeCell ref="C87:C92"/>
-    <mergeCell ref="C93:C99"/>
-    <mergeCell ref="C100:C103"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11955,27 +11738,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="183"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="177"/>
       <c r="G1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
@@ -12002,11 +11785,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="120" customHeight="1">
-      <c r="A4" s="160"/>
+      <c r="A4" s="158"/>
       <c r="B4" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="165"/>
+      <c r="C4" s="159"/>
       <c r="D4" s="48" t="s">
         <v>335</v>
       </c>
@@ -12019,11 +11802,11 @@
       <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" ht="104.4">
-      <c r="A5" s="160"/>
+      <c r="A5" s="158"/>
       <c r="B5" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="165"/>
+      <c r="C5" s="159"/>
       <c r="D5" s="48" t="s">
         <v>338</v>
       </c>
@@ -12036,11 +11819,11 @@
       <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" ht="100.2" customHeight="1">
-      <c r="A6" s="160"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="165"/>
+      <c r="C6" s="159"/>
       <c r="D6" s="48" t="s">
         <v>337</v>
       </c>
@@ -12052,11 +11835,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="60" customHeight="1">
-      <c r="A7" s="160"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="102"/>
+      <c r="C7" s="162"/>
       <c r="D7" s="48" t="s">
         <v>344</v>
       </c>
@@ -12071,11 +11854,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A8" s="160"/>
+      <c r="A8" s="158"/>
       <c r="B8" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="162"/>
       <c r="D8" s="48" t="s">
         <v>345</v>
       </c>
@@ -12090,11 +11873,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="90" customHeight="1">
-      <c r="A9" s="160"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="162"/>
       <c r="D9" s="48" t="s">
         <v>259</v>
       </c>
@@ -12106,11 +11889,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="66" customHeight="1">
-      <c r="A10" s="160"/>
+      <c r="A10" s="158"/>
       <c r="B10" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="162"/>
       <c r="D10" s="48" t="s">
         <v>312</v>
       </c>
@@ -12125,7 +11908,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="34.799999999999997">
-      <c r="A11" s="160"/>
+      <c r="A11" s="158"/>
       <c r="B11" s="30" t="s">
         <v>118</v>
       </c>
@@ -12143,11 +11926,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="79.5" customHeight="1">
-      <c r="A12" s="160"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="165" t="s">
+      <c r="C12" s="159" t="s">
         <v>121</v>
       </c>
       <c r="D12" s="48" t="s">
@@ -12161,11 +11944,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A13" s="160"/>
+      <c r="A13" s="158"/>
       <c r="B13" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="165"/>
+      <c r="C13" s="159"/>
       <c r="D13" s="48" t="s">
         <v>261</v>
       </c>
@@ -12180,11 +11963,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A14" s="160"/>
+      <c r="A14" s="158"/>
       <c r="B14" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="165"/>
+      <c r="C14" s="159"/>
       <c r="D14" s="48" t="s">
         <v>262</v>
       </c>
@@ -12196,11 +11979,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A15" s="160"/>
+      <c r="A15" s="158"/>
       <c r="B15" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="165"/>
+      <c r="C15" s="159"/>
       <c r="D15" s="48" t="s">
         <v>349</v>
       </c>
@@ -12212,11 +11995,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A16" s="160"/>
+      <c r="A16" s="158"/>
       <c r="B16" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="165" t="s">
+      <c r="C16" s="159" t="s">
         <v>448</v>
       </c>
       <c r="D16" s="48" t="s">
@@ -12230,11 +12013,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A17" s="160"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="165"/>
+      <c r="C17" s="159"/>
       <c r="D17" s="49" t="s">
         <v>264</v>
       </c>
@@ -12246,11 +12029,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A18" s="160"/>
+      <c r="A18" s="158"/>
       <c r="B18" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="165"/>
+      <c r="C18" s="159"/>
       <c r="D18" s="49" t="s">
         <v>265</v>
       </c>
@@ -12262,11 +12045,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A19" s="160"/>
+      <c r="A19" s="158"/>
       <c r="B19" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="C19" s="165"/>
+      <c r="C19" s="159"/>
       <c r="D19" s="49" t="s">
         <v>266</v>
       </c>
@@ -12278,13 +12061,13 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A20" s="169" t="s">
+      <c r="A20" s="163" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="C20" s="171" t="s">
+      <c r="C20" s="165" t="s">
         <v>164</v>
       </c>
       <c r="D20" s="41" t="s">
@@ -12298,11 +12081,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A21" s="170"/>
+      <c r="A21" s="164"/>
       <c r="B21" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C21" s="145"/>
+      <c r="C21" s="151"/>
       <c r="D21" s="41" t="s">
         <v>268</v>
       </c>
@@ -12314,11 +12097,11 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A22" s="170"/>
+      <c r="A22" s="164"/>
       <c r="B22" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="C22" s="145"/>
+      <c r="C22" s="151"/>
       <c r="D22" s="41" t="s">
         <v>269</v>
       </c>
@@ -12330,11 +12113,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A23" s="170"/>
+      <c r="A23" s="164"/>
       <c r="B23" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C23" s="145"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="42" t="s">
         <v>270</v>
       </c>
@@ -12346,11 +12129,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A24" s="170"/>
+      <c r="A24" s="164"/>
       <c r="B24" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="C24" s="145"/>
+      <c r="C24" s="151"/>
       <c r="D24" s="42" t="s">
         <v>129</v>
       </c>
@@ -12362,11 +12145,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" s="21" customFormat="1" ht="40.200000000000003" customHeight="1">
-      <c r="A25" s="170"/>
+      <c r="A25" s="164"/>
       <c r="B25" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="C25" s="145"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="41" t="s">
         <v>271</v>
       </c>
@@ -12378,11 +12161,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A26" s="170"/>
+      <c r="A26" s="164"/>
       <c r="B26" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="C26" s="145"/>
+      <c r="C26" s="151"/>
       <c r="D26" s="42" t="s">
         <v>272</v>
       </c>
@@ -12394,11 +12177,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A27" s="170"/>
+      <c r="A27" s="164"/>
       <c r="B27" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="C27" s="145"/>
+      <c r="C27" s="151"/>
       <c r="D27" s="42" t="s">
         <v>273</v>
       </c>
@@ -12410,11 +12193,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A28" s="170"/>
+      <c r="A28" s="164"/>
       <c r="B28" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="C28" s="145"/>
+      <c r="C28" s="151"/>
       <c r="D28" s="42" t="s">
         <v>274</v>
       </c>
@@ -12426,11 +12209,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A29" s="170"/>
+      <c r="A29" s="164"/>
       <c r="B29" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="C29" s="145"/>
+      <c r="C29" s="151"/>
       <c r="D29" s="42" t="s">
         <v>133</v>
       </c>
@@ -12442,11 +12225,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A30" s="170"/>
+      <c r="A30" s="164"/>
       <c r="B30" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="C30" s="145"/>
+      <c r="C30" s="151"/>
       <c r="D30" s="42" t="s">
         <v>277</v>
       </c>
@@ -12456,16 +12239,16 @@
       <c r="F30" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G30" s="172" t="s">
+      <c r="G30" s="166" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A31" s="170"/>
+      <c r="A31" s="164"/>
       <c r="B31" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="C31" s="145"/>
+      <c r="C31" s="151"/>
       <c r="D31" s="42" t="s">
         <v>278</v>
       </c>
@@ -12475,14 +12258,14 @@
       <c r="F31" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G31" s="172"/>
+      <c r="G31" s="166"/>
     </row>
     <row r="32" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A32" s="170"/>
+      <c r="A32" s="164"/>
       <c r="B32" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="C32" s="145"/>
+      <c r="C32" s="151"/>
       <c r="D32" s="42" t="s">
         <v>137</v>
       </c>
@@ -12492,14 +12275,14 @@
       <c r="F32" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G32" s="172"/>
+      <c r="G32" s="166"/>
     </row>
     <row r="33" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A33" s="170"/>
+      <c r="A33" s="164"/>
       <c r="B33" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="C33" s="145"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="42" t="s">
         <v>390</v>
       </c>
@@ -12509,14 +12292,14 @@
       <c r="F33" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G33" s="172"/>
+      <c r="G33" s="166"/>
     </row>
     <row r="34" spans="1:7" ht="20.399999999999999">
-      <c r="A34" s="170"/>
+      <c r="A34" s="164"/>
       <c r="B34" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="C34" s="145"/>
+      <c r="C34" s="151"/>
       <c r="D34" s="41" t="s">
         <v>394</v>
       </c>
@@ -12526,14 +12309,14 @@
       <c r="F34" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G34" s="172"/>
+      <c r="G34" s="166"/>
     </row>
     <row r="35" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A35" s="170"/>
+      <c r="A35" s="164"/>
       <c r="B35" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="C35" s="145" t="s">
+      <c r="C35" s="151" t="s">
         <v>449</v>
       </c>
       <c r="D35" s="41" t="s">
@@ -12545,14 +12328,14 @@
       <c r="F35" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="G35" s="172"/>
+      <c r="G35" s="166"/>
     </row>
     <row r="36" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A36" s="170"/>
+      <c r="A36" s="164"/>
       <c r="B36" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="C36" s="145"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="41" t="s">
         <v>268</v>
       </c>
@@ -12564,11 +12347,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A37" s="170"/>
+      <c r="A37" s="164"/>
       <c r="B37" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="C37" s="145"/>
+      <c r="C37" s="151"/>
       <c r="D37" s="41" t="s">
         <v>280</v>
       </c>
@@ -12580,11 +12363,11 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A38" s="170"/>
+      <c r="A38" s="164"/>
       <c r="B38" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C38" s="145"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="42" t="s">
         <v>129</v>
       </c>
@@ -12596,11 +12379,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A39" s="170"/>
+      <c r="A39" s="164"/>
       <c r="B39" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="C39" s="145"/>
+      <c r="C39" s="151"/>
       <c r="D39" s="41" t="s">
         <v>281</v>
       </c>
@@ -12612,11 +12395,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A40" s="170"/>
+      <c r="A40" s="164"/>
       <c r="B40" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="C40" s="145"/>
+      <c r="C40" s="151"/>
       <c r="D40" s="42" t="s">
         <v>282</v>
       </c>
@@ -12628,11 +12411,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A41" s="170"/>
+      <c r="A41" s="164"/>
       <c r="B41" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="C41" s="145"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="42" t="s">
         <v>283</v>
       </c>
@@ -12644,11 +12427,11 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A42" s="170"/>
+      <c r="A42" s="164"/>
       <c r="B42" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="C42" s="145"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="42" t="s">
         <v>284</v>
       </c>
@@ -12660,11 +12443,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A43" s="170"/>
+      <c r="A43" s="164"/>
       <c r="B43" s="30" t="s">
         <v>375</v>
       </c>
-      <c r="C43" s="145"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="41" t="s">
         <v>380</v>
       </c>
@@ -12676,11 +12459,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A44" s="170"/>
+      <c r="A44" s="164"/>
       <c r="B44" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="C44" s="145"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="42" t="s">
         <v>135</v>
       </c>
@@ -12692,11 +12475,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A45" s="170"/>
+      <c r="A45" s="164"/>
       <c r="B45" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="C45" s="145"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="42" t="s">
         <v>136</v>
       </c>
@@ -12708,11 +12491,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A46" s="170"/>
+      <c r="A46" s="164"/>
       <c r="B46" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="C46" s="145"/>
+      <c r="C46" s="151"/>
       <c r="D46" s="42" t="s">
         <v>137</v>
       </c>
@@ -12724,11 +12507,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A47" s="170"/>
+      <c r="A47" s="164"/>
       <c r="B47" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C47" s="171" t="s">
+      <c r="C47" s="165" t="s">
         <v>165</v>
       </c>
       <c r="D47" s="41" t="s">
@@ -12742,11 +12525,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A48" s="170"/>
+      <c r="A48" s="164"/>
       <c r="B48" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="C48" s="145"/>
+      <c r="C48" s="151"/>
       <c r="D48" s="41" t="s">
         <v>289</v>
       </c>
@@ -12758,11 +12541,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A49" s="170"/>
+      <c r="A49" s="164"/>
       <c r="B49" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="C49" s="145"/>
+      <c r="C49" s="151"/>
       <c r="D49" s="41" t="s">
         <v>129</v>
       </c>
@@ -12774,11 +12557,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A50" s="170"/>
+      <c r="A50" s="164"/>
       <c r="B50" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="C50" s="145"/>
+      <c r="C50" s="151"/>
       <c r="D50" s="41" t="s">
         <v>141</v>
       </c>
@@ -12790,11 +12573,11 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A51" s="170"/>
+      <c r="A51" s="164"/>
       <c r="B51" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C51" s="171" t="s">
+      <c r="C51" s="165" t="s">
         <v>166</v>
       </c>
       <c r="D51" s="41" t="s">
@@ -12808,11 +12591,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A52" s="170"/>
+      <c r="A52" s="164"/>
       <c r="B52" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="C52" s="171"/>
+      <c r="C52" s="165"/>
       <c r="D52" s="41" t="s">
         <v>268</v>
       </c>
@@ -12824,11 +12607,11 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A53" s="170"/>
+      <c r="A53" s="164"/>
       <c r="B53" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="C53" s="171"/>
+      <c r="C53" s="165"/>
       <c r="D53" s="41" t="s">
         <v>292</v>
       </c>
@@ -12840,11 +12623,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A54" s="170"/>
+      <c r="A54" s="164"/>
       <c r="B54" s="30" t="s">
         <v>397</v>
       </c>
-      <c r="C54" s="171"/>
+      <c r="C54" s="165"/>
       <c r="D54" s="42" t="s">
         <v>128</v>
       </c>
@@ -12856,11 +12639,11 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A55" s="170"/>
+      <c r="A55" s="164"/>
       <c r="B55" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="C55" s="171"/>
+      <c r="C55" s="165"/>
       <c r="D55" s="42" t="s">
         <v>129</v>
       </c>
@@ -12872,11 +12655,11 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A56" s="170"/>
+      <c r="A56" s="164"/>
       <c r="B56" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="C56" s="171"/>
+      <c r="C56" s="165"/>
       <c r="D56" s="42" t="s">
         <v>130</v>
       </c>
@@ -12888,11 +12671,11 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A57" s="170"/>
+      <c r="A57" s="164"/>
       <c r="B57" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="C57" s="171"/>
+      <c r="C57" s="165"/>
       <c r="D57" s="42" t="s">
         <v>131</v>
       </c>
@@ -12904,11 +12687,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A58" s="170"/>
+      <c r="A58" s="164"/>
       <c r="B58" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="C58" s="171"/>
+      <c r="C58" s="165"/>
       <c r="D58" s="42" t="s">
         <v>132</v>
       </c>
@@ -12920,11 +12703,11 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A59" s="170"/>
+      <c r="A59" s="164"/>
       <c r="B59" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="C59" s="171"/>
+      <c r="C59" s="165"/>
       <c r="D59" s="42" t="s">
         <v>139</v>
       </c>
@@ -12936,11 +12719,11 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A60" s="170"/>
+      <c r="A60" s="164"/>
       <c r="B60" s="30" t="s">
         <v>403</v>
       </c>
-      <c r="C60" s="171"/>
+      <c r="C60" s="165"/>
       <c r="D60" s="42" t="s">
         <v>140</v>
       </c>
@@ -12952,11 +12735,11 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A61" s="170"/>
+      <c r="A61" s="164"/>
       <c r="B61" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="C61" s="171"/>
+      <c r="C61" s="165"/>
       <c r="D61" s="42" t="s">
         <v>392</v>
       </c>
@@ -12968,11 +12751,11 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A62" s="170"/>
+      <c r="A62" s="164"/>
       <c r="B62" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="C62" s="171"/>
+      <c r="C62" s="165"/>
       <c r="D62" s="42" t="s">
         <v>133</v>
       </c>
@@ -12984,11 +12767,11 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A63" s="170"/>
+      <c r="A63" s="164"/>
       <c r="B63" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="C63" s="171"/>
+      <c r="C63" s="165"/>
       <c r="D63" s="42" t="s">
         <v>134</v>
       </c>
@@ -13000,11 +12783,11 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A64" s="170"/>
+      <c r="A64" s="164"/>
       <c r="B64" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="C64" s="171"/>
+      <c r="C64" s="165"/>
       <c r="D64" s="42" t="s">
         <v>393</v>
       </c>
@@ -13016,11 +12799,11 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A65" s="170"/>
+      <c r="A65" s="164"/>
       <c r="B65" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="C65" s="171"/>
+      <c r="C65" s="165"/>
       <c r="D65" s="42" t="s">
         <v>135</v>
       </c>
@@ -13032,7 +12815,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="33" customHeight="1">
-      <c r="A66" s="114"/>
+      <c r="A66" s="178"/>
       <c r="B66" s="30" t="s">
         <v>506</v>
       </c>
@@ -13050,11 +12833,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="33" customHeight="1">
-      <c r="A67" s="114"/>
+      <c r="A67" s="178"/>
       <c r="B67" s="30" t="s">
         <v>503</v>
       </c>
-      <c r="C67" s="104" t="s">
+      <c r="C67" s="123" t="s">
         <v>487</v>
       </c>
       <c r="D67" s="41" t="s">
@@ -13068,11 +12851,11 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="33" customHeight="1">
-      <c r="A68" s="114"/>
+      <c r="A68" s="178"/>
       <c r="B68" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="C68" s="164"/>
+      <c r="C68" s="121"/>
       <c r="D68" s="41" t="s">
         <v>148</v>
       </c>
@@ -13084,11 +12867,11 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A69" s="114"/>
+      <c r="A69" s="178"/>
       <c r="B69" s="30" t="s">
         <v>415</v>
       </c>
-      <c r="C69" s="106"/>
+      <c r="C69" s="124"/>
       <c r="D69" s="42" t="s">
         <v>149</v>
       </c>
@@ -13100,7 +12883,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="52.2">
-      <c r="A70" s="108"/>
+      <c r="A70" s="110"/>
       <c r="B70" s="30" t="s">
         <v>441</v>
       </c>
@@ -13118,7 +12901,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="99" customHeight="1">
-      <c r="A71" s="108"/>
+      <c r="A71" s="110"/>
       <c r="B71" s="30" t="s">
         <v>442</v>
       </c>
@@ -13136,11 +12919,11 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A72" s="108"/>
+      <c r="A72" s="110"/>
       <c r="B72" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="C72" s="104" t="s">
+      <c r="C72" s="123" t="s">
         <v>489</v>
       </c>
       <c r="D72" s="48" t="s">
@@ -13154,11 +12937,11 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="33" customHeight="1">
-      <c r="A73" s="108"/>
+      <c r="A73" s="110"/>
       <c r="B73" s="30" t="s">
         <v>491</v>
       </c>
-      <c r="C73" s="106"/>
+      <c r="C73" s="124"/>
       <c r="D73" s="48" t="s">
         <v>256</v>
       </c>
@@ -13170,11 +12953,11 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="33" customHeight="1">
-      <c r="A74" s="108"/>
+      <c r="A74" s="110"/>
       <c r="B74" s="30" t="s">
         <v>493</v>
       </c>
-      <c r="C74" s="104" t="s">
+      <c r="C74" s="123" t="s">
         <v>492</v>
       </c>
       <c r="D74" s="41" t="s">
@@ -13188,11 +12971,11 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="33" customHeight="1">
-      <c r="A75" s="180"/>
+      <c r="A75" s="179"/>
       <c r="B75" s="30" t="s">
         <v>494</v>
       </c>
-      <c r="C75" s="106"/>
+      <c r="C75" s="124"/>
       <c r="D75" s="41" t="s">
         <v>446</v>
       </c>
@@ -13204,13 +12987,13 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A76" s="98" t="s">
+      <c r="A76" s="181" t="s">
         <v>183</v>
       </c>
       <c r="B76" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="C76" s="165" t="s">
+      <c r="C76" s="159" t="s">
         <v>150</v>
       </c>
       <c r="D76" s="48" t="s">
@@ -13222,11 +13005,11 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A77" s="99"/>
+      <c r="A77" s="170"/>
       <c r="B77" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="C77" s="165"/>
+      <c r="C77" s="159"/>
       <c r="D77" s="50" t="s">
         <v>296</v>
       </c>
@@ -13236,11 +13019,11 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A78" s="99"/>
+      <c r="A78" s="170"/>
       <c r="B78" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="C78" s="165"/>
+      <c r="C78" s="159"/>
       <c r="D78" s="49" t="s">
         <v>151</v>
       </c>
@@ -13250,11 +13033,11 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A79" s="99"/>
+      <c r="A79" s="170"/>
       <c r="B79" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="C79" s="165"/>
+      <c r="C79" s="159"/>
       <c r="D79" s="48" t="s">
         <v>297</v>
       </c>
@@ -13264,11 +13047,11 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A80" s="99"/>
+      <c r="A80" s="170"/>
       <c r="B80" s="33" t="s">
         <v>419</v>
       </c>
-      <c r="C80" s="165"/>
+      <c r="C80" s="159"/>
       <c r="D80" s="49" t="s">
         <v>426</v>
       </c>
@@ -13278,11 +13061,11 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A81" s="99"/>
+      <c r="A81" s="170"/>
       <c r="B81" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="C81" s="165"/>
+      <c r="C81" s="159"/>
       <c r="D81" s="49" t="s">
         <v>152</v>
       </c>
@@ -13292,11 +13075,11 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="60" customHeight="1">
-      <c r="A82" s="99"/>
+      <c r="A82" s="170"/>
       <c r="B82" s="33" t="s">
         <v>427</v>
       </c>
-      <c r="C82" s="165" t="s">
+      <c r="C82" s="159" t="s">
         <v>158</v>
       </c>
       <c r="D82" s="48" t="s">
@@ -13308,11 +13091,11 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="20.399999999999999">
-      <c r="A83" s="99"/>
+      <c r="A83" s="170"/>
       <c r="B83" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="C83" s="165"/>
+      <c r="C83" s="159"/>
       <c r="D83" s="48" t="s">
         <v>159</v>
       </c>
@@ -13322,11 +13105,11 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A84" s="99"/>
+      <c r="A84" s="170"/>
       <c r="B84" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="C84" s="165"/>
+      <c r="C84" s="159"/>
       <c r="D84" s="48" t="s">
         <v>299</v>
       </c>
@@ -13336,11 +13119,11 @@
       </c>
     </row>
     <row r="85" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A85" s="99"/>
+      <c r="A85" s="170"/>
       <c r="B85" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="C85" s="165"/>
+      <c r="C85" s="159"/>
       <c r="D85" s="48" t="s">
         <v>300</v>
       </c>
@@ -13350,11 +13133,11 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A86" s="99"/>
+      <c r="A86" s="170"/>
       <c r="B86" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C86" s="165"/>
+      <c r="C86" s="159"/>
       <c r="D86" s="48" t="s">
         <v>161</v>
       </c>
@@ -13364,11 +13147,11 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A87" s="99"/>
+      <c r="A87" s="170"/>
       <c r="B87" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="C87" s="165"/>
+      <c r="C87" s="159"/>
       <c r="D87" s="48" t="s">
         <v>302</v>
       </c>
@@ -13378,11 +13161,11 @@
       </c>
     </row>
     <row r="88" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A88" s="99"/>
+      <c r="A88" s="170"/>
       <c r="B88" s="33" t="s">
         <v>436</v>
       </c>
-      <c r="C88" s="165"/>
+      <c r="C88" s="159"/>
       <c r="D88" s="48" t="s">
         <v>303</v>
       </c>
@@ -13392,7 +13175,7 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="52.2">
-      <c r="A89" s="160" t="s">
+      <c r="A89" s="158" t="s">
         <v>469</v>
       </c>
       <c r="B89" s="32" t="s">
@@ -13410,7 +13193,7 @@
       </c>
     </row>
     <row r="90" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A90" s="160"/>
+      <c r="A90" s="158"/>
       <c r="B90" s="32" t="s">
         <v>437</v>
       </c>
@@ -13426,7 +13209,7 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="126" customHeight="1">
-      <c r="A91" s="160"/>
+      <c r="A91" s="158"/>
       <c r="B91" s="32" t="s">
         <v>438</v>
       </c>
@@ -13442,7 +13225,7 @@
       </c>
     </row>
     <row r="92" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A92" s="160"/>
+      <c r="A92" s="158"/>
       <c r="B92" s="32" t="s">
         <v>439</v>
       </c>
@@ -13458,13 +13241,13 @@
       </c>
     </row>
     <row r="93" spans="1:7" ht="69.599999999999994">
-      <c r="A93" s="175" t="s">
+      <c r="A93" s="182" t="s">
         <v>468</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="C93" s="145" t="s">
+      <c r="C93" s="151" t="s">
         <v>313</v>
       </c>
       <c r="D93" s="51" t="s">
@@ -13478,11 +13261,11 @@
       </c>
     </row>
     <row r="94" spans="1:7" ht="52.2">
-      <c r="A94" s="176"/>
+      <c r="A94" s="183"/>
       <c r="B94" s="25" t="s">
         <v>451</v>
       </c>
-      <c r="C94" s="145"/>
+      <c r="C94" s="151"/>
       <c r="D94" s="51" t="s">
         <v>460</v>
       </c>
@@ -13494,11 +13277,11 @@
       </c>
     </row>
     <row r="95" spans="1:7" ht="129" customHeight="1">
-      <c r="A95" s="176"/>
+      <c r="A95" s="183"/>
       <c r="B95" s="25" t="s">
         <v>452</v>
       </c>
-      <c r="C95" s="178"/>
+      <c r="C95" s="185"/>
       <c r="D95" s="51" t="s">
         <v>461</v>
       </c>
@@ -13510,11 +13293,11 @@
       </c>
     </row>
     <row r="96" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A96" s="177"/>
+      <c r="A96" s="184"/>
       <c r="B96" s="25" t="s">
         <v>453</v>
       </c>
-      <c r="C96" s="179"/>
+      <c r="C96" s="186"/>
       <c r="D96" s="48" t="s">
         <v>501</v>
       </c>
@@ -13529,7 +13312,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="87">
-      <c r="A97" s="107" t="s">
+      <c r="A97" s="109" t="s">
         <v>315</v>
       </c>
       <c r="B97" s="25" t="s">
@@ -13549,11 +13332,11 @@
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="108"/>
+      <c r="A98" s="110"/>
       <c r="B98" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="C98" s="174" t="s">
+      <c r="C98" s="180" t="s">
         <v>316</v>
       </c>
       <c r="D98" s="52" t="s">
@@ -13567,11 +13350,11 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="123" customHeight="1">
-      <c r="A99" s="108"/>
+      <c r="A99" s="110"/>
       <c r="B99" s="53" t="s">
         <v>455</v>
       </c>
-      <c r="C99" s="174"/>
+      <c r="C99" s="180"/>
       <c r="D99" s="64" t="s">
         <v>499</v>
       </c>
@@ -13583,7 +13366,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" ht="156.6">
-      <c r="A100" s="108"/>
+      <c r="A100" s="110"/>
       <c r="B100" s="53" t="s">
         <v>465</v>
       </c>
@@ -13601,7 +13384,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="34.799999999999997">
-      <c r="A101" s="161"/>
+      <c r="A101" s="167"/>
       <c r="B101" s="54" t="s">
         <v>457</v>
       </c>
@@ -13620,6 +13403,25 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="A76:A88"/>
+    <mergeCell ref="C76:C81"/>
+    <mergeCell ref="C82:C88"/>
+    <mergeCell ref="A89:A92"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="C93:C96"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A20:A65"/>
+    <mergeCell ref="C20:C34"/>
+    <mergeCell ref="G30:G35"/>
+    <mergeCell ref="C35:C46"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C51:C65"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -13628,25 +13430,6 @@
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C16:C19"/>
-    <mergeCell ref="A20:A65"/>
-    <mergeCell ref="C20:C34"/>
-    <mergeCell ref="G30:G35"/>
-    <mergeCell ref="C35:C46"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="C51:C65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="A76:A88"/>
-    <mergeCell ref="C76:C81"/>
-    <mergeCell ref="C82:C88"/>
-    <mergeCell ref="A89:A92"/>
-    <mergeCell ref="A93:A96"/>
-    <mergeCell ref="C93:C96"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13669,27 +13452,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="120"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="101"/>
       <c r="G1" s="22" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="39.9" customHeight="1">
-      <c r="A2" s="122" t="s">
+      <c r="A2" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="124" t="s">
+      <c r="B2" s="104"/>
+      <c r="C2" s="105" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="120"/>
+      <c r="D2" s="101"/>
       <c r="E2" s="29" t="s">
         <v>0</v>
       </c>
@@ -13716,11 +13499,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="104.4">
-      <c r="A4" s="160"/>
+      <c r="A4" s="158"/>
       <c r="B4" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="165"/>
+      <c r="C4" s="159"/>
       <c r="D4" s="48" t="s">
         <v>338</v>
       </c>
@@ -13733,11 +13516,11 @@
       <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" ht="121.8">
-      <c r="A5" s="160"/>
+      <c r="A5" s="158"/>
       <c r="B5" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="165"/>
+      <c r="C5" s="159"/>
       <c r="D5" s="48" t="s">
         <v>336</v>
       </c>
@@ -13750,11 +13533,11 @@
       <c r="G5" s="24"/>
     </row>
     <row r="6" spans="1:7" ht="100.2" customHeight="1">
-      <c r="A6" s="160"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="165"/>
+      <c r="C6" s="159"/>
       <c r="D6" s="48" t="s">
         <v>337</v>
       </c>
@@ -13766,11 +13549,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A7" s="160"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="102"/>
+      <c r="C7" s="162"/>
       <c r="D7" s="48" t="s">
         <v>257</v>
       </c>
@@ -13782,11 +13565,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="60" customHeight="1">
-      <c r="A8" s="160"/>
+      <c r="A8" s="158"/>
       <c r="B8" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="162"/>
       <c r="D8" s="48" t="s">
         <v>258</v>
       </c>
@@ -13798,11 +13581,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="90" customHeight="1">
-      <c r="A9" s="160"/>
+      <c r="A9" s="158"/>
       <c r="B9" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="162"/>
       <c r="D9" s="48" t="s">
         <v>259</v>
       </c>
@@ -13814,11 +13597,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="66" customHeight="1">
-      <c r="A10" s="160"/>
+      <c r="A10" s="158"/>
       <c r="B10" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="162"/>
       <c r="D10" s="48" t="s">
         <v>312</v>
       </c>
@@ -13833,11 +13616,11 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="49.5" customHeight="1">
-      <c r="A11" s="160"/>
+      <c r="A11" s="158"/>
       <c r="B11" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="103"/>
+      <c r="C11" s="187"/>
       <c r="D11" s="48" t="s">
         <v>346</v>
       </c>
@@ -13849,11 +13632,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="34.799999999999997">
-      <c r="A12" s="160"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="165" t="s">
+      <c r="C12" s="159" t="s">
         <v>447</v>
       </c>
       <c r="D12" s="48" t="s">
@@ -13865,11 +13648,11 @@
       <c r="F12" s="40"/>
     </row>
     <row r="13" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A13" s="160"/>
+      <c r="A13" s="158"/>
       <c r="B13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="165"/>
+      <c r="C13" s="159"/>
       <c r="D13" s="48" t="s">
         <v>444</v>
       </c>
@@ -13881,11 +13664,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="79.5" customHeight="1">
-      <c r="A14" s="160"/>
+      <c r="A14" s="158"/>
       <c r="B14" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="165" t="s">
+      <c r="C14" s="159" t="s">
         <v>121</v>
       </c>
       <c r="D14" s="48" t="s">
@@ -13899,11 +13682,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A15" s="160"/>
+      <c r="A15" s="158"/>
       <c r="B15" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="165"/>
+      <c r="C15" s="159"/>
       <c r="D15" s="48" t="s">
         <v>261</v>
       </c>
@@ -13918,11 +13701,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="79.95" customHeight="1">
-      <c r="A16" s="160"/>
+      <c r="A16" s="158"/>
       <c r="B16" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="165"/>
+      <c r="C16" s="159"/>
       <c r="D16" s="48" t="s">
         <v>262</v>
       </c>
@@ -13934,11 +13717,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A17" s="160"/>
+      <c r="A17" s="158"/>
       <c r="B17" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="165"/>
+      <c r="C17" s="159"/>
       <c r="D17" s="48" t="s">
         <v>349</v>
       </c>
@@ -13950,11 +13733,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A18" s="160"/>
+      <c r="A18" s="158"/>
       <c r="B18" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="165" t="s">
+      <c r="C18" s="159" t="s">
         <v>448</v>
       </c>
       <c r="D18" s="48" t="s">
@@ -13968,11 +13751,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A19" s="160"/>
+      <c r="A19" s="158"/>
       <c r="B19" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="165"/>
+      <c r="C19" s="159"/>
       <c r="D19" s="49" t="s">
         <v>264</v>
       </c>
@@ -13984,11 +13767,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A20" s="160"/>
+      <c r="A20" s="158"/>
       <c r="B20" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="165"/>
+      <c r="C20" s="159"/>
       <c r="D20" s="49" t="s">
         <v>265</v>
       </c>
@@ -14000,11 +13783,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A21" s="160"/>
+      <c r="A21" s="158"/>
       <c r="B21" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="C21" s="165"/>
+      <c r="C21" s="159"/>
       <c r="D21" s="49" t="s">
         <v>266</v>
       </c>
@@ -14016,13 +13799,13 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A22" s="169" t="s">
+      <c r="A22" s="163" t="s">
         <v>181</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="C22" s="171" t="s">
+      <c r="C22" s="165" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="41" t="s">
@@ -14036,11 +13819,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A23" s="170"/>
+      <c r="A23" s="164"/>
       <c r="B23" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="C23" s="145"/>
+      <c r="C23" s="151"/>
       <c r="D23" s="41" t="s">
         <v>268</v>
       </c>
@@ -14052,11 +13835,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A24" s="170"/>
+      <c r="A24" s="164"/>
       <c r="B24" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="C24" s="145"/>
+      <c r="C24" s="151"/>
       <c r="D24" s="41" t="s">
         <v>269</v>
       </c>
@@ -14068,11 +13851,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A25" s="170"/>
+      <c r="A25" s="164"/>
       <c r="B25" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="C25" s="145"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="42" t="s">
         <v>270</v>
       </c>
@@ -14084,11 +13867,11 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A26" s="170"/>
+      <c r="A26" s="164"/>
       <c r="B26" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="C26" s="145"/>
+      <c r="C26" s="151"/>
       <c r="D26" s="42" t="s">
         <v>129</v>
       </c>
@@ -14100,11 +13883,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="21" customFormat="1" ht="40.200000000000003" customHeight="1">
-      <c r="A27" s="170"/>
+      <c r="A27" s="164"/>
       <c r="B27" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="C27" s="145"/>
+      <c r="C27" s="151"/>
       <c r="D27" s="41" t="s">
         <v>271</v>
       </c>
@@ -14116,11 +13899,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A28" s="170"/>
+      <c r="A28" s="164"/>
       <c r="B28" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="C28" s="145"/>
+      <c r="C28" s="151"/>
       <c r="D28" s="42" t="s">
         <v>272</v>
       </c>
@@ -14132,11 +13915,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A29" s="170"/>
+      <c r="A29" s="164"/>
       <c r="B29" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="145"/>
+      <c r="C29" s="151"/>
       <c r="D29" s="42" t="s">
         <v>273</v>
       </c>
@@ -14148,11 +13931,11 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A30" s="170"/>
+      <c r="A30" s="164"/>
       <c r="B30" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="C30" s="145"/>
+      <c r="C30" s="151"/>
       <c r="D30" s="42" t="s">
         <v>274</v>
       </c>
@@ -14164,11 +13947,11 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A31" s="170"/>
+      <c r="A31" s="164"/>
       <c r="B31" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="C31" s="145"/>
+      <c r="C31" s="151"/>
       <c r="D31" s="42" t="s">
         <v>133</v>
       </c>
@@ -14180,11 +13963,11 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A32" s="170"/>
+      <c r="A32" s="164"/>
       <c r="B32" s="30" t="s">
         <v>361</v>
       </c>
-      <c r="C32" s="145"/>
+      <c r="C32" s="151"/>
       <c r="D32" s="42" t="s">
         <v>277</v>
       </c>
@@ -14194,16 +13977,16 @@
       <c r="F32" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G32" s="172" t="s">
+      <c r="G32" s="166" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A33" s="170"/>
+      <c r="A33" s="164"/>
       <c r="B33" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="C33" s="145"/>
+      <c r="C33" s="151"/>
       <c r="D33" s="42" t="s">
         <v>278</v>
       </c>
@@ -14213,14 +13996,14 @@
       <c r="F33" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G33" s="172"/>
+      <c r="G33" s="166"/>
     </row>
     <row r="34" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A34" s="170"/>
+      <c r="A34" s="164"/>
       <c r="B34" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="C34" s="145"/>
+      <c r="C34" s="151"/>
       <c r="D34" s="42" t="s">
         <v>137</v>
       </c>
@@ -14230,14 +14013,14 @@
       <c r="F34" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G34" s="172"/>
+      <c r="G34" s="166"/>
     </row>
     <row r="35" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A35" s="170"/>
+      <c r="A35" s="164"/>
       <c r="B35" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="C35" s="145"/>
+      <c r="C35" s="151"/>
       <c r="D35" s="42" t="s">
         <v>390</v>
       </c>
@@ -14247,14 +14030,14 @@
       <c r="F35" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G35" s="172"/>
+      <c r="G35" s="166"/>
     </row>
     <row r="36" spans="1:7" ht="20.399999999999999">
-      <c r="A36" s="170"/>
+      <c r="A36" s="164"/>
       <c r="B36" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="C36" s="145"/>
+      <c r="C36" s="151"/>
       <c r="D36" s="41" t="s">
         <v>394</v>
       </c>
@@ -14264,14 +14047,14 @@
       <c r="F36" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G36" s="172"/>
+      <c r="G36" s="166"/>
     </row>
     <row r="37" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A37" s="170"/>
+      <c r="A37" s="164"/>
       <c r="B37" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="C37" s="145" t="s">
+      <c r="C37" s="151" t="s">
         <v>449</v>
       </c>
       <c r="D37" s="41" t="s">
@@ -14283,14 +14066,14 @@
       <c r="F37" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="G37" s="172"/>
+      <c r="G37" s="166"/>
     </row>
     <row r="38" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A38" s="170"/>
+      <c r="A38" s="164"/>
       <c r="B38" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="C38" s="145"/>
+      <c r="C38" s="151"/>
       <c r="D38" s="41" t="s">
         <v>268</v>
       </c>
@@ -14302,11 +14085,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A39" s="170"/>
+      <c r="A39" s="164"/>
       <c r="B39" s="30" t="s">
         <v>368</v>
       </c>
-      <c r="C39" s="145"/>
+      <c r="C39" s="151"/>
       <c r="D39" s="41" t="s">
         <v>280</v>
       </c>
@@ -14318,11 +14101,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A40" s="170"/>
+      <c r="A40" s="164"/>
       <c r="B40" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="C40" s="145"/>
+      <c r="C40" s="151"/>
       <c r="D40" s="42" t="s">
         <v>129</v>
       </c>
@@ -14334,11 +14117,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A41" s="170"/>
+      <c r="A41" s="164"/>
       <c r="B41" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="C41" s="145"/>
+      <c r="C41" s="151"/>
       <c r="D41" s="41" t="s">
         <v>281</v>
       </c>
@@ -14350,11 +14133,11 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A42" s="170"/>
+      <c r="A42" s="164"/>
       <c r="B42" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="C42" s="145"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="42" t="s">
         <v>282</v>
       </c>
@@ -14366,11 +14149,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A43" s="170"/>
+      <c r="A43" s="164"/>
       <c r="B43" s="30" t="s">
         <v>373</v>
       </c>
-      <c r="C43" s="145"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="42" t="s">
         <v>283</v>
       </c>
@@ -14382,11 +14165,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A44" s="170"/>
+      <c r="A44" s="164"/>
       <c r="B44" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="C44" s="145"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="42" t="s">
         <v>284</v>
       </c>
@@ -14398,11 +14181,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="40.200000000000003" customHeight="1">
-      <c r="A45" s="170"/>
+      <c r="A45" s="164"/>
       <c r="B45" s="30" t="s">
         <v>375</v>
       </c>
-      <c r="C45" s="145"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="41" t="s">
         <v>380</v>
       </c>
@@ -14414,11 +14197,11 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A46" s="170"/>
+      <c r="A46" s="164"/>
       <c r="B46" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="C46" s="145"/>
+      <c r="C46" s="151"/>
       <c r="D46" s="42" t="s">
         <v>135</v>
       </c>
@@ -14430,11 +14213,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A47" s="170"/>
+      <c r="A47" s="164"/>
       <c r="B47" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="C47" s="145"/>
+      <c r="C47" s="151"/>
       <c r="D47" s="42" t="s">
         <v>136</v>
       </c>
@@ -14446,11 +14229,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A48" s="170"/>
+      <c r="A48" s="164"/>
       <c r="B48" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="C48" s="145"/>
+      <c r="C48" s="151"/>
       <c r="D48" s="42" t="s">
         <v>137</v>
       </c>
@@ -14462,11 +14245,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A49" s="170"/>
+      <c r="A49" s="164"/>
       <c r="B49" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="C49" s="171" t="s">
+      <c r="C49" s="165" t="s">
         <v>165</v>
       </c>
       <c r="D49" s="41" t="s">
@@ -14480,11 +14263,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A50" s="170"/>
+      <c r="A50" s="164"/>
       <c r="B50" s="30" t="s">
         <v>382</v>
       </c>
-      <c r="C50" s="145"/>
+      <c r="C50" s="151"/>
       <c r="D50" s="41" t="s">
         <v>289</v>
       </c>
@@ -14496,11 +14279,11 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A51" s="170"/>
+      <c r="A51" s="164"/>
       <c r="B51" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="C51" s="145"/>
+      <c r="C51" s="151"/>
       <c r="D51" s="41" t="s">
         <v>129</v>
       </c>
@@ -14512,11 +14295,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A52" s="170"/>
+      <c r="A52" s="164"/>
       <c r="B52" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="C52" s="145"/>
+      <c r="C52" s="151"/>
       <c r="D52" s="41" t="s">
         <v>141</v>
       </c>
@@ -14528,11 +14311,11 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A53" s="170"/>
+      <c r="A53" s="164"/>
       <c r="B53" s="30" t="s">
         <v>310</v>
       </c>
-      <c r="C53" s="171" t="s">
+      <c r="C53" s="165" t="s">
         <v>166</v>
       </c>
       <c r="D53" s="41" t="s">
@@ -14546,11 +14329,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A54" s="170"/>
+      <c r="A54" s="164"/>
       <c r="B54" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="C54" s="171"/>
+      <c r="C54" s="165"/>
       <c r="D54" s="41" t="s">
         <v>268</v>
       </c>
@@ -14562,11 +14345,11 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A55" s="170"/>
+      <c r="A55" s="164"/>
       <c r="B55" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="C55" s="171"/>
+      <c r="C55" s="165"/>
       <c r="D55" s="41" t="s">
         <v>292</v>
       </c>
@@ -14578,11 +14361,11 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A56" s="170"/>
+      <c r="A56" s="164"/>
       <c r="B56" s="30" t="s">
         <v>397</v>
       </c>
-      <c r="C56" s="171"/>
+      <c r="C56" s="165"/>
       <c r="D56" s="42" t="s">
         <v>128</v>
       </c>
@@ -14594,11 +14377,11 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A57" s="170"/>
+      <c r="A57" s="164"/>
       <c r="B57" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="C57" s="171"/>
+      <c r="C57" s="165"/>
       <c r="D57" s="42" t="s">
         <v>129</v>
       </c>
@@ -14610,11 +14393,11 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A58" s="170"/>
+      <c r="A58" s="164"/>
       <c r="B58" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="C58" s="171"/>
+      <c r="C58" s="165"/>
       <c r="D58" s="42" t="s">
         <v>130</v>
       </c>
@@ -14626,11 +14409,11 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A59" s="170"/>
+      <c r="A59" s="164"/>
       <c r="B59" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="C59" s="171"/>
+      <c r="C59" s="165"/>
       <c r="D59" s="42" t="s">
         <v>131</v>
       </c>
@@ -14642,11 +14425,11 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A60" s="170"/>
+      <c r="A60" s="164"/>
       <c r="B60" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="C60" s="171"/>
+      <c r="C60" s="165"/>
       <c r="D60" s="42" t="s">
         <v>132</v>
       </c>
@@ -14658,11 +14441,11 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A61" s="170"/>
+      <c r="A61" s="164"/>
       <c r="B61" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="C61" s="171"/>
+      <c r="C61" s="165"/>
       <c r="D61" s="42" t="s">
         <v>139</v>
       </c>
@@ -14674,11 +14457,11 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A62" s="170"/>
+      <c r="A62" s="164"/>
       <c r="B62" s="30" t="s">
         <v>403</v>
       </c>
-      <c r="C62" s="171"/>
+      <c r="C62" s="165"/>
       <c r="D62" s="42" t="s">
         <v>140</v>
       </c>
@@ -14690,11 +14473,11 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A63" s="170"/>
+      <c r="A63" s="164"/>
       <c r="B63" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="C63" s="171"/>
+      <c r="C63" s="165"/>
       <c r="D63" s="42" t="s">
         <v>392</v>
       </c>
@@ -14706,11 +14489,11 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A64" s="170"/>
+      <c r="A64" s="164"/>
       <c r="B64" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="C64" s="171"/>
+      <c r="C64" s="165"/>
       <c r="D64" s="42" t="s">
         <v>133</v>
       </c>
@@ -14722,11 +14505,11 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A65" s="170"/>
+      <c r="A65" s="164"/>
       <c r="B65" s="30" t="s">
         <v>406</v>
       </c>
-      <c r="C65" s="171"/>
+      <c r="C65" s="165"/>
       <c r="D65" s="42" t="s">
         <v>134</v>
       </c>
@@ -14738,11 +14521,11 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A66" s="170"/>
+      <c r="A66" s="164"/>
       <c r="B66" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="C66" s="171"/>
+      <c r="C66" s="165"/>
       <c r="D66" s="42" t="s">
         <v>393</v>
       </c>
@@ -14754,11 +14537,11 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A67" s="170"/>
+      <c r="A67" s="164"/>
       <c r="B67" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="C67" s="171"/>
+      <c r="C67" s="165"/>
       <c r="D67" s="42" t="s">
         <v>135</v>
       </c>
@@ -14770,11 +14553,11 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A68" s="170"/>
+      <c r="A68" s="164"/>
       <c r="B68" s="30" t="s">
         <v>409</v>
       </c>
-      <c r="C68" s="171"/>
+      <c r="C68" s="165"/>
       <c r="D68" s="42" t="s">
         <v>136</v>
       </c>
@@ -14786,11 +14569,11 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A69" s="170"/>
+      <c r="A69" s="164"/>
       <c r="B69" s="30" t="s">
         <v>410</v>
       </c>
-      <c r="C69" s="171"/>
+      <c r="C69" s="165"/>
       <c r="D69" s="42" t="s">
         <v>137</v>
       </c>
@@ -14802,11 +14585,11 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A70" s="170"/>
+      <c r="A70" s="164"/>
       <c r="B70" s="30" t="s">
         <v>411</v>
       </c>
-      <c r="C70" s="171"/>
+      <c r="C70" s="165"/>
       <c r="D70" s="42" t="s">
         <v>138</v>
       </c>
@@ -14818,7 +14601,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="66" customHeight="1">
-      <c r="A71" s="162" t="s">
+      <c r="A71" s="168" t="s">
         <v>182</v>
       </c>
       <c r="B71" s="30" t="s">
@@ -14838,7 +14621,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A72" s="163"/>
+      <c r="A72" s="169"/>
       <c r="B72" s="30" t="s">
         <v>505</v>
       </c>
@@ -14856,7 +14639,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A73" s="163"/>
+      <c r="A73" s="169"/>
       <c r="B73" s="30" t="s">
         <v>507</v>
       </c>
@@ -14874,11 +14657,11 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="33" customHeight="1">
-      <c r="A74" s="163"/>
+      <c r="A74" s="169"/>
       <c r="B74" s="30" t="s">
         <v>508</v>
       </c>
-      <c r="C74" s="171" t="s">
+      <c r="C74" s="165" t="s">
         <v>488</v>
       </c>
       <c r="D74" s="41" t="s">
@@ -14892,11 +14675,11 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="132" customHeight="1">
-      <c r="A75" s="184"/>
+      <c r="A75" s="188"/>
       <c r="B75" s="30" t="s">
         <v>509</v>
       </c>
-      <c r="C75" s="145"/>
+      <c r="C75" s="151"/>
       <c r="D75" s="41" t="s">
         <v>294</v>
       </c>
@@ -14908,7 +14691,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="49.5" customHeight="1">
-      <c r="A76" s="150" t="s">
+      <c r="A76" s="145" t="s">
         <v>467</v>
       </c>
       <c r="B76" s="30" t="s">
@@ -14928,11 +14711,11 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A77" s="151"/>
+      <c r="A77" s="146"/>
       <c r="B77" s="30" t="s">
         <v>490</v>
       </c>
-      <c r="C77" s="104" t="s">
+      <c r="C77" s="123" t="s">
         <v>489</v>
       </c>
       <c r="D77" s="48" t="s">
@@ -14946,11 +14729,11 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="33" customHeight="1">
-      <c r="A78" s="151"/>
+      <c r="A78" s="146"/>
       <c r="B78" s="30" t="s">
         <v>491</v>
       </c>
-      <c r="C78" s="106"/>
+      <c r="C78" s="124"/>
       <c r="D78" s="48" t="s">
         <v>256</v>
       </c>
@@ -14962,7 +14745,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="33" customHeight="1">
-      <c r="A79" s="185"/>
+      <c r="A79" s="189"/>
       <c r="B79" s="30" t="s">
         <v>494</v>
       </c>
@@ -14978,13 +14761,13 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A80" s="98" t="s">
+      <c r="A80" s="181" t="s">
         <v>183</v>
       </c>
       <c r="B80" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="C80" s="165" t="s">
+      <c r="C80" s="159" t="s">
         <v>150</v>
       </c>
       <c r="D80" s="48" t="s">
@@ -14996,11 +14779,11 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A81" s="99"/>
+      <c r="A81" s="170"/>
       <c r="B81" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="C81" s="165"/>
+      <c r="C81" s="159"/>
       <c r="D81" s="50" t="s">
         <v>296</v>
       </c>
@@ -15010,11 +14793,11 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A82" s="99"/>
+      <c r="A82" s="170"/>
       <c r="B82" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="C82" s="165"/>
+      <c r="C82" s="159"/>
       <c r="D82" s="49" t="s">
         <v>151</v>
       </c>
@@ -15024,11 +14807,11 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A83" s="99"/>
+      <c r="A83" s="170"/>
       <c r="B83" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="C83" s="165"/>
+      <c r="C83" s="159"/>
       <c r="D83" s="48" t="s">
         <v>297</v>
       </c>
@@ -15038,11 +14821,11 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A84" s="99"/>
+      <c r="A84" s="170"/>
       <c r="B84" s="33" t="s">
         <v>419</v>
       </c>
-      <c r="C84" s="165"/>
+      <c r="C84" s="159"/>
       <c r="D84" s="49" t="s">
         <v>426</v>
       </c>
@@ -15052,11 +14835,11 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="25.2" customHeight="1">
-      <c r="A85" s="99"/>
+      <c r="A85" s="170"/>
       <c r="B85" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="C85" s="165"/>
+      <c r="C85" s="159"/>
       <c r="D85" s="49" t="s">
         <v>152</v>
       </c>
@@ -15066,11 +14849,11 @@
       </c>
     </row>
     <row r="86" spans="1:6" ht="60" customHeight="1">
-      <c r="A86" s="99"/>
+      <c r="A86" s="170"/>
       <c r="B86" s="33" t="s">
         <v>427</v>
       </c>
-      <c r="C86" s="165" t="s">
+      <c r="C86" s="159" t="s">
         <v>158</v>
       </c>
       <c r="D86" s="48" t="s">
@@ -15082,11 +14865,11 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="20.399999999999999">
-      <c r="A87" s="99"/>
+      <c r="A87" s="170"/>
       <c r="B87" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="C87" s="165"/>
+      <c r="C87" s="159"/>
       <c r="D87" s="48" t="s">
         <v>159</v>
       </c>
@@ -15096,11 +14879,11 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A88" s="99"/>
+      <c r="A88" s="170"/>
       <c r="B88" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="C88" s="165"/>
+      <c r="C88" s="159"/>
       <c r="D88" s="48" t="s">
         <v>299</v>
       </c>
@@ -15110,11 +14893,11 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A89" s="99"/>
+      <c r="A89" s="170"/>
       <c r="B89" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="C89" s="165"/>
+      <c r="C89" s="159"/>
       <c r="D89" s="48" t="s">
         <v>300</v>
       </c>
@@ -15124,11 +14907,11 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A90" s="99"/>
+      <c r="A90" s="170"/>
       <c r="B90" s="33" t="s">
         <v>434</v>
       </c>
-      <c r="C90" s="165"/>
+      <c r="C90" s="159"/>
       <c r="D90" s="48" t="s">
         <v>161</v>
       </c>
@@ -15138,11 +14921,11 @@
       </c>
     </row>
     <row r="91" spans="1:6" ht="40.200000000000003" customHeight="1">
-      <c r="A91" s="99"/>
+      <c r="A91" s="170"/>
       <c r="B91" s="33" t="s">
         <v>435</v>
       </c>
-      <c r="C91" s="165"/>
+      <c r="C91" s="159"/>
       <c r="D91" s="48" t="s">
         <v>302</v>
       </c>
@@ -15152,11 +14935,11 @@
       </c>
     </row>
     <row r="92" spans="1:6" ht="79.95" customHeight="1">
-      <c r="A92" s="99"/>
+      <c r="A92" s="170"/>
       <c r="B92" s="33" t="s">
         <v>436</v>
       </c>
-      <c r="C92" s="165"/>
+      <c r="C92" s="159"/>
       <c r="D92" s="48" t="s">
         <v>303</v>
       </c>
@@ -15166,7 +14949,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="52.2">
-      <c r="A93" s="160" t="s">
+      <c r="A93" s="158" t="s">
         <v>469</v>
       </c>
       <c r="B93" s="32" t="s">
@@ -15184,7 +14967,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" ht="126" customHeight="1">
-      <c r="A94" s="160"/>
+      <c r="A94" s="158"/>
       <c r="B94" s="32" t="s">
         <v>438</v>
       </c>
@@ -15200,7 +14983,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="87">
-      <c r="A95" s="107" t="s">
+      <c r="A95" s="109" t="s">
         <v>315</v>
       </c>
       <c r="B95" s="25" t="s">
@@ -15220,11 +15003,11 @@
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="108"/>
+      <c r="A96" s="110"/>
       <c r="B96" s="53" t="s">
         <v>463</v>
       </c>
-      <c r="C96" s="174" t="s">
+      <c r="C96" s="180" t="s">
         <v>316</v>
       </c>
       <c r="D96" s="52" t="s">
@@ -15238,11 +15021,11 @@
       </c>
     </row>
     <row r="97" spans="1:7" ht="174">
-      <c r="A97" s="108"/>
+      <c r="A97" s="110"/>
       <c r="B97" s="53" t="s">
         <v>456</v>
       </c>
-      <c r="C97" s="174"/>
+      <c r="C97" s="180"/>
       <c r="D97" s="52" t="s">
         <v>464</v>
       </c>
@@ -15257,7 +15040,7 @@
       </c>
     </row>
     <row r="98" spans="1:7" ht="156.6">
-      <c r="A98" s="108"/>
+      <c r="A98" s="110"/>
       <c r="B98" s="53" t="s">
         <v>465</v>
       </c>
@@ -15275,7 +15058,7 @@
       </c>
     </row>
     <row r="99" spans="1:7" ht="34.799999999999997">
-      <c r="A99" s="161"/>
+      <c r="A99" s="167"/>
       <c r="B99" s="53" t="s">
         <v>457</v>
       </c>
@@ -15294,21 +15077,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A4:A21"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="A22:A70"/>
-    <mergeCell ref="C22:C36"/>
-    <mergeCell ref="G32:G37"/>
-    <mergeCell ref="C37:C48"/>
-    <mergeCell ref="C49:C52"/>
-    <mergeCell ref="C53:C70"/>
     <mergeCell ref="A93:A94"/>
     <mergeCell ref="A95:A99"/>
     <mergeCell ref="C96:C97"/>
@@ -15319,6 +15087,21 @@
     <mergeCell ref="A80:A92"/>
     <mergeCell ref="C80:C85"/>
     <mergeCell ref="C86:C92"/>
+    <mergeCell ref="A22:A70"/>
+    <mergeCell ref="C22:C36"/>
+    <mergeCell ref="G32:G37"/>
+    <mergeCell ref="C37:C48"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="C53:C70"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A4:A21"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C18:C21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
